--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="439" documentId="13_ncr:1_{28BD4CF4-A877-4909-81F4-E5A6CEB4DAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{786ADAC5-2C06-47B5-9484-E080A5D19676}"/>
+  <xr:revisionPtr revIDLastSave="546" documentId="13_ncr:1_{28BD4CF4-A877-4909-81F4-E5A6CEB4DAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B67E80F-22F5-4B50-A032-F5EEB78A776D}"/>
   <bookViews>
-    <workbookView xWindow="15360" yWindow="0" windowWidth="15360" windowHeight="16680" activeTab="4" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="179">
   <si>
     <t>#</t>
   </si>
@@ -311,18 +311,6 @@
     <t>Model Order AR 3</t>
   </si>
   <si>
-    <t>NN Architecture</t>
-  </si>
-  <si>
-    <t>NN Para 1</t>
-  </si>
-  <si>
-    <t>PINN Architecture</t>
-  </si>
-  <si>
-    <t>PINN Para 1</t>
-  </si>
-  <si>
     <t>Model Order POD</t>
   </si>
   <si>
@@ -344,18 +332,9 @@
     <t>pod</t>
   </si>
   <si>
-    <t>nn</t>
-  </si>
-  <si>
-    <t>pinn</t>
-  </si>
-  <si>
     <t>Slope Spezific Resistance</t>
   </si>
   <si>
-    <t>Offset Spezific Resistance</t>
-  </si>
-  <si>
     <t>Contact Resistance</t>
   </si>
   <si>
@@ -366,15 +345,6 @@
   </si>
   <si>
     <t>Backward Losses</t>
-  </si>
-  <si>
-    <t>Adaptive Capacitance</t>
-  </si>
-  <si>
-    <t>Convection Resistance</t>
-  </si>
-  <si>
-    <t>ther</t>
   </si>
   <si>
     <t>Initialise Zero</t>
@@ -552,10 +522,6 @@
 2) Estimated</t>
   </si>
   <si>
-    <t>1) Stability not constraint
-2) Stability enforced by N4SID</t>
-  </si>
-  <si>
     <t>sta</t>
   </si>
   <si>
@@ -575,6 +541,84 @@
   </si>
   <si>
     <t>eng</t>
+  </si>
+  <si>
+    <t>TF Init</t>
+  </si>
+  <si>
+    <t>TF Stability</t>
+  </si>
+  <si>
+    <t>AR Init</t>
+  </si>
+  <si>
+    <t>AR Stability</t>
+  </si>
+  <si>
+    <t>mdlInit</t>
+  </si>
+  <si>
+    <t>Number of POD modes.</t>
+  </si>
+  <si>
+    <t>Lower numerical boundary</t>
+  </si>
+  <si>
+    <t>1) Stability not constraint
+2) Stability enforced</t>
+  </si>
+  <si>
+    <t>Numerical error boundary used for convergence</t>
+  </si>
+  <si>
+    <t>PDE solver:
+1) ode45 (non-stiff)
+2) ode15 (stiff)
+3) rk6
+4) euf (euler forward)
+5) eub (euler backward)
+6) tra (trapazoidal rule)</t>
+  </si>
+  <si>
+    <t>Number of substeps per solver iteration</t>
+  </si>
+  <si>
+    <t>0) not correcting losses during training
+1) correcting losses during training</t>
+  </si>
+  <si>
+    <t>0) not correcting losses during testing
+1) correcting losses during testing</t>
+  </si>
+  <si>
+    <t>bw</t>
+  </si>
+  <si>
+    <t>fw</t>
+  </si>
+  <si>
+    <t>°C</t>
+  </si>
+  <si>
+    <t>Reference temperature for loss calculation</t>
+  </si>
+  <si>
+    <t>Temperature independent contact resistance</t>
+  </si>
+  <si>
+    <t>Ohm</t>
+  </si>
+  <si>
+    <t>Tref</t>
+  </si>
+  <si>
+    <t>Rcon</t>
+  </si>
+  <si>
+    <t>Resistance change per 1 K temperature increase</t>
+  </si>
+  <si>
+    <t>Rslope</t>
   </si>
 </sst>
 </file>
@@ -989,7 +1033,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1081,13 +1125,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1098,6 +1145,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1114,6 +1164,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1476,11 +1530,11 @@
       <c r="F13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J13" s="44" t="s">
+      <c r="J13" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="45"/>
-      <c r="L13" s="46"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="47"/>
     </row>
     <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
@@ -1604,19 +1658,19 @@
     </row>
     <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="D2" s="26" t="s">
         <v>80</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F2" s="6">
         <v>1</v>
@@ -1627,13 +1681,13 @@
     </row>
     <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B3" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D3" s="26" t="s">
         <v>22</v>
@@ -1650,16 +1704,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>49</v>
@@ -1673,19 +1727,19 @@
     </row>
     <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F5" s="6">
         <v>0</v>
@@ -1957,14 +2011,16 @@
     </row>
     <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="25"/>
+        <v>103</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>63</v>
+      </c>
       <c r="C2" s="5" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="E2" s="26" t="s">
         <v>48</v>
@@ -1978,14 +2034,16 @@
     </row>
     <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" s="25"/>
+        <v>104</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>63</v>
+      </c>
       <c r="C3" s="5" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E3" s="26" t="s">
         <v>48</v>
@@ -1999,161 +2057,177 @@
     </row>
     <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" s="25"/>
+        <v>107</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>63</v>
+      </c>
       <c r="C4" s="5" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F4" s="11">
         <v>0</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="25"/>
+        <v>122</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>63</v>
+      </c>
       <c r="C5" s="5" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F5" s="11">
         <v>0</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="25"/>
+        <v>123</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>63</v>
+      </c>
       <c r="C6" s="5" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F6" s="11">
         <v>0</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="B7" s="25"/>
+        <v>124</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>63</v>
+      </c>
       <c r="C7" s="5" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F7" s="11">
         <v>0</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B8" s="25"/>
+        <v>125</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>63</v>
+      </c>
       <c r="C8" s="5" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F8" s="11">
         <v>0</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="5" t="s">
-        <v>146</v>
-      </c>
       <c r="D9" s="26" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F9" s="11">
         <v>0</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10" s="25"/>
+        <v>127</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>63</v>
+      </c>
       <c r="C10" s="5" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F10" s="11">
         <v>0</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="25"/>
+        <v>113</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>63</v>
+      </c>
       <c r="C11" s="5" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>48</v>
@@ -2327,7 +2401,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
@@ -2367,14 +2441,18 @@
       <c r="B2" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="8"/>
+      <c r="C2" s="8" t="s">
+        <v>164</v>
+      </c>
       <c r="D2" s="28" t="s">
         <v>65</v>
       </c>
       <c r="E2" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="9"/>
+      <c r="F2" s="44">
+        <v>1E-3</v>
+      </c>
       <c r="G2" s="31" t="s">
         <v>16</v>
       </c>
@@ -2386,33 +2464,41 @@
       <c r="B3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="5"/>
+      <c r="C3" s="5" t="s">
+        <v>162</v>
+      </c>
       <c r="D3" s="26" t="s">
         <v>20</v>
       </c>
       <c r="E3" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="43">
+        <v>9.9999999999999998E-13</v>
+      </c>
       <c r="G3" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="5"/>
+      <c r="C4" s="5" t="s">
+        <v>165</v>
+      </c>
       <c r="D4" s="26" t="s">
         <v>61</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
       <c r="G4" s="29" t="s">
         <v>16</v>
       </c>
@@ -2424,14 +2510,18 @@
       <c r="B5" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="7" t="s">
+        <v>166</v>
+      </c>
       <c r="D5" s="27" t="s">
         <v>60</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="10"/>
+      <c r="F5" s="10">
+        <v>20</v>
+      </c>
       <c r="G5" s="30" t="s">
         <v>16</v>
       </c>
@@ -2447,7 +2537,7 @@
         <v>70</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E6" s="28" t="s">
         <v>48</v>
@@ -2472,8 +2562,12 @@
       <c r="D7" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="27"/>
-      <c r="F7" s="10"/>
+      <c r="E7" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0</v>
+      </c>
       <c r="G7" s="30" t="s">
         <v>69</v>
       </c>
@@ -2486,10 +2580,10 @@
         <v>79</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>48</v>
@@ -2509,10 +2603,10 @@
         <v>79</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>48</v>
@@ -2532,10 +2626,10 @@
         <v>79</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>48</v>
@@ -2555,7 +2649,7 @@
         <v>79</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D11" s="26" t="s">
         <v>61</v>
@@ -2578,7 +2672,7 @@
         <v>79</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D12" s="26" t="s">
         <v>80</v>
@@ -2601,9 +2695,15 @@
         <v>79</v>
       </c>
       <c r="C13" s="5"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="6"/>
+      <c r="D13" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="6">
+        <v>1</v>
+      </c>
       <c r="G13" s="29"/>
     </row>
     <row r="14" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -2614,10 +2714,10 @@
         <v>79</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>48</v>
@@ -2634,11 +2734,11 @@
         <v>81</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="28" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E15" s="28" t="s">
         <v>48</v>
@@ -2655,11 +2755,11 @@
         <v>82</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="26" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E16" s="28" t="s">
         <v>48</v>
@@ -2676,11 +2776,11 @@
         <v>83</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="26" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="E17" s="28" t="s">
         <v>48</v>
@@ -2697,10 +2797,10 @@
         <v>76</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D18" s="26" t="s">
         <v>80</v>
@@ -2717,28 +2817,42 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C19" s="5"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="6"/>
+      <c r="D19" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" s="6">
+        <v>1</v>
+      </c>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="10"/>
+        <v>91</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="10">
+        <v>1</v>
+      </c>
       <c r="G20" s="30"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -2746,11 +2860,11 @@
         <v>84</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="28" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E21" s="28" t="s">
         <v>48</v>
@@ -2767,11 +2881,11 @@
         <v>85</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="26" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E22" s="28" t="s">
         <v>48</v>
@@ -2788,11 +2902,11 @@
         <v>86</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="26" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="E23" s="28" t="s">
         <v>48</v>
@@ -2809,10 +2923,10 @@
         <v>76</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D24" s="26" t="s">
         <v>80</v>
@@ -2829,28 +2943,42 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C25" s="5"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="6"/>
+      <c r="D25" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="6">
+        <v>1</v>
+      </c>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="14" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="10">
+        <v>1</v>
+      </c>
       <c r="G26" s="30"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -2858,151 +2986,137 @@
         <v>87</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" s="8"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="31"/>
-    </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="9">
+        <v>3</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="30"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
+      <c r="B28" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="6">
+        <v>1</v>
+      </c>
+      <c r="G28" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="B29" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="31"/>
+      <c r="B29" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="6">
+        <v>10</v>
+      </c>
+      <c r="G29" s="29" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="14" t="s">
         <v>90</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="30"/>
+        <v>93</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="42">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="G30" s="30" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" s="28" t="s">
-        <v>97</v>
-      </c>
+      <c r="A31" s="12"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="8"/>
-      <c r="D31" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="E31" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31" s="9">
-        <v>3</v>
-      </c>
-      <c r="G31" s="31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="E32" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" s="6">
-        <v>1</v>
-      </c>
-      <c r="G32" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A33" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33" s="6">
-        <v>10</v>
-      </c>
-      <c r="G33" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B34" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="E34" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="F34" s="43">
-        <v>0.99990000000000001</v>
-      </c>
-      <c r="G34" s="30" t="s">
-        <v>18</v>
-      </c>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="31"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="13"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="29"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="13"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="29"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="13"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="29"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="12"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="31"/>
+      <c r="A35" s="13"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="29"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>
@@ -3067,63 +3181,34 @@
       <c r="F42" s="6"/>
       <c r="G42" s="29"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="29"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="26"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="6"/>
-      <c r="G44" s="29"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="6"/>
-      <c r="G45" s="29"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="26"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="29"/>
-    </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7 F2:F5 F19:F20 F25:F30 F13 F35:F46" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F31:F42" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8 F6 F15:F17 F21:F23 F31" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8 F6 F15:F17 F21:F23 F27" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F9:F12 F14 F24 F18" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F9:F14 F18:F20 F24:F26" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
       <formula1>"1, 2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F32" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F28" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
       <formula1>"1, 2, 3"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F33" xr:uid="{42D8AC35-50A5-40BC-BBFA-BE08B273A500}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F29" xr:uid="{42D8AC35-50A5-40BC-BBFA-BE08B273A500}">
       <formula1>1</formula1>
       <formula2>20</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F34" xr:uid="{2B8FFCC1-6704-4765-8AD4-006A185633FA}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F30 F2:F3" xr:uid="{2B8FFCC1-6704-4765-8AD4-006A185633FA}">
       <formula1>0</formula1>
       <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5" xr:uid="{758AA2D1-1396-4D76-9384-11AC5DDB0A43}">
+      <formula1>1</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{3A0BB9DE-DDAB-4BD6-B6E2-43F1FC222D8A}">
+      <formula1>"1, 2, 3, 4, 5, 6"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3132,7 +3217,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
@@ -3180,7 +3265,9 @@
       <c r="E2" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="6"/>
+      <c r="F2" s="6">
+        <v>1</v>
+      </c>
       <c r="G2" s="29" t="s">
         <v>16</v>
       </c>
@@ -3201,7 +3288,9 @@
       <c r="E3" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
       <c r="G3" s="29" t="s">
         <v>16</v>
       </c>
@@ -3222,7 +3311,9 @@
       <c r="E4" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
       <c r="G4" s="29" t="s">
         <v>16</v>
       </c>
@@ -3237,11 +3328,15 @@
       <c r="C5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="26"/>
+      <c r="D5" s="26" t="s">
+        <v>65</v>
+      </c>
       <c r="E5" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="43">
+        <v>1E-3</v>
+      </c>
       <c r="G5" s="29" t="s">
         <v>16</v>
       </c>
@@ -3256,12 +3351,16 @@
       <c r="C6" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="39"/>
+      <c r="D6" s="39" t="s">
+        <v>20</v>
+      </c>
       <c r="E6" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="41"/>
-      <c r="G6" s="42" t="s">
+      <c r="F6" s="43">
+        <v>9.9999999999999998E-13</v>
+      </c>
+      <c r="G6" s="41" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3281,109 +3380,149 @@
       <c r="E7" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="10"/>
+      <c r="F7" s="42">
+        <v>0.01</v>
+      </c>
       <c r="G7" s="30" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B8" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="31"/>
+      <c r="C8" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="48">
+        <v>3.9300000000000003E-3</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="29"/>
+      <c r="C9" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="29"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C10" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" s="11">
+        <v>20</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="29"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B12" s="26" t="s">
+      <c r="C11" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="29"/>
-    </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="30"/>
+      <c r="C12" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="10">
+        <v>0</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="13"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="29"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="31"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="29"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>108</v>
-      </c>
+      <c r="A15" s="13"/>
+      <c r="B15" s="26"/>
       <c r="C15" s="5"/>
       <c r="D15" s="26"/>
       <c r="E15" s="26"/>
@@ -3480,39 +3619,25 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="29"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="29"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="29"/>
-    </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{697C1F42-E75F-4B7B-8981-25DC1390010D}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F4" xr:uid="{697C1F42-E75F-4B7B-8981-25DC1390010D}">
+      <formula1>"1, 2, 3, 4"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F6" xr:uid="{E37BC251-E8D8-40F6-9FAF-822D8D9984D3}">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F8" xr:uid="{A51E82E7-1822-482E-8232-D090CCE8FF42}">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11:F12" xr:uid="{BEBAF08F-EDA5-4C4D-BDED-841DA49ED29D}">
       <formula1>"0, 1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F28" xr:uid="{C68A9EBE-58BC-4060-95BF-8B9C15EAA08F}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F9" xr:uid="{A50DEA59-3116-48A6-9A6B-FEC85B06DD9A}">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F25" xr:uid="{C68A9EBE-58BC-4060-95BF-8B9C15EAA08F}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="546" documentId="13_ncr:1_{28BD4CF4-A877-4909-81F4-E5A6CEB4DAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B67E80F-22F5-4B50-A032-F5EEB78A776D}"/>
+  <xr:revisionPtr revIDLastSave="550" documentId="13_ncr:1_{28BD4CF4-A877-4909-81F4-E5A6CEB4DAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C74AD05-957D-4453-BA3E-E077AD4CB0F8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="2" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -397,12 +397,6 @@
     <t>Data Separation</t>
   </si>
   <si>
-    <t>Method for separating the data into training, testing, and validation sets:
-1) File based, each set has its own data file
-2) ID based, each set has a unique ID from one file
-3) Ratio based, one file is spilt into different parts</t>
-  </si>
-  <si>
     <t>sep</t>
   </si>
   <si>
@@ -619,6 +613,13 @@
   </si>
   <si>
     <t>Rslope</t>
+  </si>
+  <si>
+    <t>Method for separating the data into training, testing, and validation sets:
+1) File based, each set has its own data file
+2) Sheet based, each set has its own excel sheet
+3) ID based, each set has a unique ID from one file
+4) Ratio based, one file is spilt into different parts</t>
   </si>
 </sst>
 </file>
@@ -1137,6 +1138,9 @@
     <xf numFmtId="11" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1145,9 +1149,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1530,11 +1531,11 @@
       <c r="F13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J13" s="45" t="s">
+      <c r="J13" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="46"/>
-      <c r="L13" s="47"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="48"/>
     </row>
     <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
@@ -1664,13 +1665,13 @@
         <v>63</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D2" s="26" t="s">
         <v>80</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F2" s="6">
         <v>1</v>
@@ -1687,7 +1688,7 @@
         <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D3" s="26" t="s">
         <v>22</v>
@@ -1710,10 +1711,10 @@
         <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>49</v>
@@ -1733,13 +1734,13 @@
         <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>119</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>120</v>
       </c>
       <c r="F5" s="6">
         <v>0</v>
@@ -2075,21 +2076,21 @@
         <v>0</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>112</v>
@@ -2098,21 +2099,21 @@
         <v>0</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>112</v>
@@ -2121,21 +2122,21 @@
         <v>0</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>112</v>
@@ -2144,21 +2145,21 @@
         <v>0</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>112</v>
@@ -2167,21 +2168,21 @@
         <v>0</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>112</v>
@@ -2190,21 +2191,21 @@
         <v>0</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>112</v>
@@ -2213,10 +2214,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>113</v>
       </c>
@@ -2224,16 +2225,16 @@
         <v>63</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="26" t="s">
         <v>114</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>115</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>48</v>
       </c>
       <c r="F11" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="29" t="s">
         <v>16</v>
@@ -2384,15 +2385,18 @@
       <c r="G27" s="29"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12:F27" xr:uid="{1216C920-F66D-486D-9FEC-8D6771F4D7DB}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3 F11" xr:uid="{F91803D7-6ECC-462D-BB39-BF39F2230D48}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3" xr:uid="{F91803D7-6ECC-462D-BB39-BF39F2230D48}">
       <formula1>"1, 2, 3"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{83ADC3B0-4649-4A01-9D68-DDE40B796C91}">
       <formula1>"1, 2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11" xr:uid="{73C737E8-6BB1-4480-A19A-B64640252DD2}">
+      <formula1>"1, 2, 3, 4"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2442,7 +2446,7 @@
         <v>63</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D2" s="28" t="s">
         <v>65</v>
@@ -2465,7 +2469,7 @@
         <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D3" s="26" t="s">
         <v>20</v>
@@ -2488,7 +2492,7 @@
         <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>61</v>
@@ -2511,7 +2515,7 @@
         <v>63</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D5" s="27" t="s">
         <v>60</v>
@@ -2537,7 +2541,7 @@
         <v>70</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E6" s="28" t="s">
         <v>48</v>
@@ -2580,10 +2584,10 @@
         <v>79</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>139</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>140</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>48</v>
@@ -2603,10 +2607,10 @@
         <v>79</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D9" s="26" t="s">
         <v>144</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>145</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>48</v>
@@ -2626,10 +2630,10 @@
         <v>79</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D10" s="26" t="s">
         <v>146</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>147</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>48</v>
@@ -2649,7 +2653,7 @@
         <v>79</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" s="26" t="s">
         <v>61</v>
@@ -2672,7 +2676,7 @@
         <v>79</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D12" s="26" t="s">
         <v>80</v>
@@ -2696,7 +2700,7 @@
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>48</v>
@@ -2714,10 +2718,10 @@
         <v>79</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>48</v>
@@ -2738,7 +2742,7 @@
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E15" s="28" t="s">
         <v>48</v>
@@ -2759,7 +2763,7 @@
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E16" s="28" t="s">
         <v>48</v>
@@ -2780,7 +2784,7 @@
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E17" s="28" t="s">
         <v>48</v>
@@ -2800,7 +2804,7 @@
         <v>91</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D18" s="26" t="s">
         <v>80</v>
@@ -2817,14 +2821,14 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>91</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E19" s="26" t="s">
         <v>48</v>
@@ -2836,16 +2840,16 @@
     </row>
     <row r="20" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B20" s="27" t="s">
         <v>91</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>48</v>
@@ -2864,7 +2868,7 @@
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E21" s="28" t="s">
         <v>48</v>
@@ -2885,7 +2889,7 @@
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E22" s="28" t="s">
         <v>48</v>
@@ -2906,7 +2910,7 @@
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E23" s="28" t="s">
         <v>48</v>
@@ -2926,7 +2930,7 @@
         <v>92</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D24" s="26" t="s">
         <v>80</v>
@@ -2943,14 +2947,14 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>92</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E25" s="26" t="s">
         <v>48</v>
@@ -2962,16 +2966,16 @@
     </row>
     <row r="26" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="14" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B26" s="27" t="s">
         <v>92</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E26" s="27" t="s">
         <v>48</v>
@@ -2989,10 +2993,10 @@
         <v>93</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E27" s="28" t="s">
         <v>48</v>
@@ -3012,7 +3016,7 @@
         <v>93</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D28" s="26" t="s">
         <v>62</v>
@@ -3035,10 +3039,10 @@
         <v>93</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D29" s="26" t="s">
         <v>152</v>
-      </c>
-      <c r="D29" s="26" t="s">
-        <v>153</v>
       </c>
       <c r="E29" s="26" t="s">
         <v>48</v>
@@ -3058,10 +3062,10 @@
         <v>93</v>
       </c>
       <c r="C30" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D30" s="27" t="s">
         <v>154</v>
-      </c>
-      <c r="D30" s="27" t="s">
-        <v>155</v>
       </c>
       <c r="E30" s="27" t="s">
         <v>55</v>
@@ -3395,15 +3399,15 @@
         <v>23</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>177</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>178</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="45">
         <v>3.9300000000000003E-3</v>
       </c>
       <c r="G8" s="31" t="s">
@@ -3418,10 +3422,10 @@
         <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>49</v>
@@ -3430,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -3441,10 +3445,10 @@
         <v>23</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>112</v>
@@ -3453,7 +3457,7 @@
         <v>20</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -3464,10 +3468,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>48</v>
@@ -3487,10 +3491,10 @@
         <v>23</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="27" t="s">
         <v>168</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>169</v>
       </c>
       <c r="E12" s="27" t="s">
         <v>48</v>

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="550" documentId="13_ncr:1_{28BD4CF4-A877-4909-81F4-E5A6CEB4DAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C74AD05-957D-4453-BA3E-E077AD4CB0F8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9401A4D0-A7B1-45F1-8F27-AF31A074385B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="2" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-28920" yWindow="-1470" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -1034,7 +1034,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1150,9 +1150,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1167,14 +1170,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1212,7 +1211,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1318,7 +1317,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1460,7 +1459,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1469,17 +1468,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA655AC4-52E1-45C0-83AC-CC64B56C05A9}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.77734375" customWidth="1"/>
-    <col min="5" max="6" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -1487,7 +1486,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1495,7 +1494,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1503,7 +1502,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1511,8 +1510,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -1537,7 +1536,7 @@
       <c r="K13" s="47"/>
       <c r="L13" s="48"/>
     </row>
-    <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -1566,7 +1565,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1578,7 +1577,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -1590,7 +1589,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>4</v>
       </c>
@@ -1602,7 +1601,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>5</v>
       </c>
@@ -1626,15 +1625,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB857B-5D2E-4BE1-B462-B4B5EEAA4370}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.21875" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -1657,14 +1656,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>99</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="49" t="s">
         <v>120</v>
       </c>
       <c r="D2" s="26" t="s">
@@ -1680,7 +1679,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>100</v>
       </c>
@@ -1703,7 +1702,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>101</v>
       </c>
@@ -1726,7 +1725,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>102</v>
       </c>
@@ -1749,7 +1748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="13"/>
       <c r="B6" s="26"/>
       <c r="C6" s="5"/>
@@ -1758,7 +1757,7 @@
       <c r="F6" s="6"/>
       <c r="G6" s="29"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
       <c r="B7" s="26"/>
       <c r="C7" s="5"/>
@@ -1767,7 +1766,7 @@
       <c r="F7" s="6"/>
       <c r="G7" s="29"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="26"/>
       <c r="C8" s="5"/>
@@ -1776,7 +1775,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
       <c r="B9" s="26"/>
       <c r="C9" s="5"/>
@@ -1785,7 +1784,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="29"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
       <c r="B10" s="26"/>
       <c r="C10" s="5"/>
@@ -1794,7 +1793,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="26"/>
       <c r="C11" s="5"/>
@@ -1803,7 +1802,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="26"/>
       <c r="C12" s="5"/>
@@ -1812,7 +1811,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="26"/>
       <c r="C13" s="5"/>
@@ -1821,7 +1820,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -1830,7 +1829,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -1839,7 +1838,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -1848,7 +1847,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -1857,7 +1856,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -1866,7 +1865,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -1875,7 +1874,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -1884,7 +1883,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -1893,7 +1892,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -1902,7 +1901,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -1911,7 +1910,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -1920,7 +1919,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -1929,7 +1928,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>
@@ -1938,7 +1937,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="26"/>
       <c r="C27" s="5"/>
@@ -1947,7 +1946,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="26"/>
       <c r="C28" s="5"/>
@@ -1979,15 +1978,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86190CFD-1D2B-4FE4-A04E-A3C453840C86}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.21875" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2010,7 +2009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>103</v>
       </c>
@@ -2033,7 +2032,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>104</v>
       </c>
@@ -2056,7 +2055,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>107</v>
       </c>
@@ -2079,7 +2078,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>121</v>
       </c>
@@ -2102,7 +2101,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>122</v>
       </c>
@@ -2125,7 +2124,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>123</v>
       </c>
@@ -2148,7 +2147,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>124</v>
       </c>
@@ -2171,7 +2170,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>125</v>
       </c>
@@ -2194,7 +2193,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>126</v>
       </c>
@@ -2217,7 +2216,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>113</v>
       </c>
@@ -2240,7 +2239,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="25"/>
       <c r="C12" s="5"/>
@@ -2249,7 +2248,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="25"/>
       <c r="C13" s="5"/>
@@ -2258,7 +2257,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="25"/>
       <c r="C14" s="5"/>
@@ -2267,7 +2266,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="25"/>
       <c r="C15" s="5"/>
@@ -2276,7 +2275,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="25"/>
       <c r="C16" s="5"/>
@@ -2285,7 +2284,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="25"/>
       <c r="C17" s="5"/>
@@ -2294,7 +2293,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="25"/>
       <c r="C18" s="5"/>
@@ -2303,7 +2302,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="25"/>
       <c r="C19" s="5"/>
@@ -2312,7 +2311,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="25"/>
       <c r="C20" s="5"/>
@@ -2321,7 +2320,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="25"/>
       <c r="C21" s="5"/>
@@ -2330,7 +2329,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="25"/>
       <c r="C22" s="5"/>
@@ -2339,7 +2338,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="25"/>
       <c r="C23" s="5"/>
@@ -2348,7 +2347,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="25"/>
       <c r="C24" s="5"/>
@@ -2357,7 +2356,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="25"/>
       <c r="C25" s="5"/>
@@ -2366,7 +2365,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="25"/>
       <c r="C26" s="5"/>
@@ -2375,7 +2374,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="25"/>
       <c r="C27" s="5"/>
@@ -2406,16 +2405,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.21875" customWidth="1"/>
-    <col min="7" max="7" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2438,7 +2437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>56</v>
       </c>
@@ -2461,7 +2460,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>57</v>
       </c>
@@ -2484,7 +2483,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
@@ -2507,7 +2506,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>59</v>
       </c>
@@ -2530,7 +2529,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>72</v>
       </c>
@@ -2553,7 +2552,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>66</v>
       </c>
@@ -2576,7 +2575,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>71</v>
       </c>
@@ -2599,7 +2598,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>73</v>
       </c>
@@ -2622,7 +2621,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>74</v>
       </c>
@@ -2645,7 +2644,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>75</v>
       </c>
@@ -2668,7 +2667,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>76</v>
       </c>
@@ -2691,7 +2690,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>77</v>
       </c>
@@ -2710,7 +2709,7 @@
       </c>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>78</v>
       </c>
@@ -2733,7 +2732,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>81</v>
       </c>
@@ -2754,7 +2753,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>82</v>
       </c>
@@ -2775,7 +2774,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>83</v>
       </c>
@@ -2796,7 +2795,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>76</v>
       </c>
@@ -2819,7 +2818,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>155</v>
       </c>
@@ -2838,7 +2837,7 @@
       </c>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>156</v>
       </c>
@@ -2859,7 +2858,7 @@
       </c>
       <c r="G20" s="30"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>84</v>
       </c>
@@ -2880,7 +2879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>85</v>
       </c>
@@ -2901,7 +2900,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>86</v>
       </c>
@@ -2922,7 +2921,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>76</v>
       </c>
@@ -2945,7 +2944,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>157</v>
       </c>
@@ -2964,7 +2963,7 @@
       </c>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>158</v>
       </c>
@@ -2985,7 +2984,7 @@
       </c>
       <c r="G26" s="30"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>87</v>
       </c>
@@ -3008,7 +3007,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>88</v>
       </c>
@@ -3031,7 +3030,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>89</v>
       </c>
@@ -3054,7 +3053,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>90</v>
       </c>
@@ -3077,7 +3076,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="28"/>
       <c r="C31" s="8"/>
@@ -3086,7 +3085,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="31"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="13"/>
       <c r="B32" s="26"/>
       <c r="C32" s="5"/>
@@ -3095,7 +3094,7 @@
       <c r="F32" s="6"/>
       <c r="G32" s="29"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>
       <c r="B33" s="26"/>
       <c r="C33" s="5"/>
@@ -3104,7 +3103,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="29"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>
       <c r="B34" s="26"/>
       <c r="C34" s="5"/>
@@ -3113,7 +3112,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="29"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="26"/>
       <c r="C35" s="5"/>
@@ -3122,7 +3121,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="29"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="13"/>
       <c r="B36" s="26"/>
       <c r="C36" s="5"/>
@@ -3131,7 +3130,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="29"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="26"/>
       <c r="C37" s="5"/>
@@ -3140,7 +3139,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="29"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="26"/>
       <c r="C38" s="5"/>
@@ -3149,7 +3148,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="29"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>
       <c r="B39" s="26"/>
       <c r="C39" s="5"/>
@@ -3158,7 +3157,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="29"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
       <c r="B40" s="26"/>
       <c r="C40" s="5"/>
@@ -3167,7 +3166,7 @@
       <c r="F40" s="6"/>
       <c r="G40" s="29"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="26"/>
       <c r="C41" s="5"/>
@@ -3176,7 +3175,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>
       <c r="B42" s="26"/>
       <c r="C42" s="5"/>
@@ -3222,15 +3221,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.21875" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -3253,7 +3252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="72.599999999999994" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>38</v>
       </c>
@@ -3276,7 +3275,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>39</v>
       </c>
@@ -3299,7 +3298,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
@@ -3322,7 +3321,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>44</v>
       </c>
@@ -3345,7 +3344,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
         <v>50</v>
       </c>
@@ -3368,7 +3367,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -3391,7 +3390,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>94</v>
       </c>
@@ -3414,7 +3413,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>95</v>
       </c>
@@ -3437,7 +3436,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>96</v>
       </c>
@@ -3460,7 +3459,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>97</v>
       </c>
@@ -3483,7 +3482,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>98</v>
       </c>
@@ -3506,7 +3505,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="26"/>
       <c r="C13" s="5"/>
@@ -3515,7 +3514,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -3524,7 +3523,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -3533,7 +3532,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -3542,7 +3541,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -3551,7 +3550,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -3560,7 +3559,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -3569,7 +3568,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -3578,7 +3577,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -3587,7 +3586,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -3596,7 +3595,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -3605,7 +3604,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -3614,7 +3613,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9401A4D0-A7B1-45F1-8F27-AF31A074385B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{9401A4D0-A7B1-45F1-8F27-AF31A074385B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EC29174-F32A-4956-87AA-9AFD8E974D87}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1470" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="182">
   <si>
     <t>#</t>
   </si>
@@ -526,9 +526,6 @@
   </si>
   <si>
     <t>Constraint for automatically chosing the number of modes.</t>
-  </si>
-  <si>
-    <t>max</t>
   </si>
   <si>
     <t>Percentag of energy captured through POD modes</t>
@@ -620,6 +617,18 @@
 2) Sheet based, each set has its own excel sheet
 3) ID based, each set has a unique ID from one file
 4) Ratio based, one file is spilt into different parts</t>
+  </si>
+  <si>
+    <t>Maximum Iteration</t>
+  </si>
+  <si>
+    <t>Maximum number of iterations for solvers</t>
+  </si>
+  <si>
+    <t>iterMax</t>
+  </si>
+  <si>
+    <t>Kmax</t>
   </si>
 </sst>
 </file>
@@ -1034,7 +1043,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1141,6 +1150,12 @@
     <xf numFmtId="10" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1150,12 +1165,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1170,10 +1182,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1211,7 +1227,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1317,7 +1333,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1459,7 +1475,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1468,17 +1484,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA655AC4-52E1-45C0-83AC-CC64B56C05A9}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.7109375" customWidth="1"/>
-    <col min="5" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.6640625" customWidth="1"/>
+    <col min="5" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -1486,7 +1502,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1494,7 +1510,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1502,7 +1518,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1510,8 +1526,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -1530,13 +1546,13 @@
       <c r="F13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J13" s="46" t="s">
+      <c r="J13" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="47"/>
-      <c r="L13" s="48"/>
-    </row>
-    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K13" s="49"/>
+      <c r="L13" s="50"/>
+    </row>
+    <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -1565,7 +1581,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1577,7 +1593,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -1589,7 +1605,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>4</v>
       </c>
@@ -1601,7 +1617,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>5</v>
       </c>
@@ -1625,15 +1641,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB857B-5D2E-4BE1-B462-B4B5EEAA4370}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -1656,14 +1672,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>99</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="49" t="s">
+      <c r="C2" s="46" t="s">
         <v>120</v>
       </c>
       <c r="D2" s="26" t="s">
@@ -1679,7 +1695,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>100</v>
       </c>
@@ -1702,7 +1718,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>101</v>
       </c>
@@ -1725,7 +1741,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>102</v>
       </c>
@@ -1748,7 +1764,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="13"/>
       <c r="B6" s="26"/>
       <c r="C6" s="5"/>
@@ -1757,7 +1773,7 @@
       <c r="F6" s="6"/>
       <c r="G6" s="29"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="13"/>
       <c r="B7" s="26"/>
       <c r="C7" s="5"/>
@@ -1766,7 +1782,7 @@
       <c r="F7" s="6"/>
       <c r="G7" s="29"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
       <c r="B8" s="26"/>
       <c r="C8" s="5"/>
@@ -1775,7 +1791,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
       <c r="B9" s="26"/>
       <c r="C9" s="5"/>
@@ -1784,7 +1800,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="29"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>
       <c r="B10" s="26"/>
       <c r="C10" s="5"/>
@@ -1793,7 +1809,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="26"/>
       <c r="C11" s="5"/>
@@ -1802,7 +1818,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="26"/>
       <c r="C12" s="5"/>
@@ -1811,7 +1827,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="26"/>
       <c r="C13" s="5"/>
@@ -1820,7 +1836,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -1829,7 +1845,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -1838,7 +1854,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -1847,7 +1863,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -1856,7 +1872,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -1865,7 +1881,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -1874,7 +1890,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -1883,7 +1899,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -1892,7 +1908,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -1901,7 +1917,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -1910,7 +1926,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -1919,7 +1935,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -1928,7 +1944,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>
@@ -1937,7 +1953,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
       <c r="B27" s="26"/>
       <c r="C27" s="5"/>
@@ -1946,7 +1962,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
       <c r="B28" s="26"/>
       <c r="C28" s="5"/>
@@ -1978,15 +1994,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86190CFD-1D2B-4FE4-A04E-A3C453840C86}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2009,7 +2025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>103</v>
       </c>
@@ -2032,7 +2048,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>104</v>
       </c>
@@ -2055,7 +2071,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>107</v>
       </c>
@@ -2078,7 +2094,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>121</v>
       </c>
@@ -2101,7 +2117,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>122</v>
       </c>
@@ -2124,7 +2140,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>123</v>
       </c>
@@ -2147,7 +2163,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>124</v>
       </c>
@@ -2170,7 +2186,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>125</v>
       </c>
@@ -2193,7 +2209,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>126</v>
       </c>
@@ -2216,7 +2232,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>113</v>
       </c>
@@ -2224,7 +2240,7 @@
         <v>63</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D11" s="26" t="s">
         <v>114</v>
@@ -2239,7 +2255,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="25"/>
       <c r="C12" s="5"/>
@@ -2248,7 +2264,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="25"/>
       <c r="C13" s="5"/>
@@ -2257,7 +2273,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="25"/>
       <c r="C14" s="5"/>
@@ -2266,7 +2282,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="25"/>
       <c r="C15" s="5"/>
@@ -2275,7 +2291,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="25"/>
       <c r="C16" s="5"/>
@@ -2284,7 +2300,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="25"/>
       <c r="C17" s="5"/>
@@ -2293,7 +2309,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="25"/>
       <c r="C18" s="5"/>
@@ -2302,7 +2318,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="25"/>
       <c r="C19" s="5"/>
@@ -2311,7 +2327,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="25"/>
       <c r="C20" s="5"/>
@@ -2320,7 +2336,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="25"/>
       <c r="C21" s="5"/>
@@ -2329,7 +2345,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="25"/>
       <c r="C22" s="5"/>
@@ -2338,7 +2354,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="25"/>
       <c r="C23" s="5"/>
@@ -2347,7 +2363,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="25"/>
       <c r="C24" s="5"/>
@@ -2356,7 +2372,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="25"/>
       <c r="C25" s="5"/>
@@ -2365,7 +2381,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="25"/>
       <c r="C26" s="5"/>
@@ -2374,7 +2390,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
       <c r="B27" s="25"/>
       <c r="C27" s="5"/>
@@ -2404,17 +2420,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
-  <dimension ref="A1:G42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G43"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2437,7 +2453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>56</v>
       </c>
@@ -2445,7 +2461,7 @@
         <v>63</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D2" s="28" t="s">
         <v>65</v>
@@ -2460,7 +2476,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>57</v>
       </c>
@@ -2468,7 +2484,7 @@
         <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D3" s="26" t="s">
         <v>20</v>
@@ -2483,7 +2499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
@@ -2491,7 +2507,7 @@
         <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>61</v>
@@ -2506,179 +2522,179 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="47">
+        <v>10000</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B6" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="D5" s="27" t="s">
+      <c r="C6" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E6" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F6" s="47">
         <v>20</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G6" s="41" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="6">
+        <v>10</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="42">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B9" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D9" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E9" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F9" s="9">
         <v>3</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G9" s="31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+    <row r="10" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B10" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C10" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D10" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E10" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F10" s="10">
         <v>0</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G10" s="30" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B11" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D11" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E11" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F11" s="9">
         <v>3</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G11" s="31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
         <v>73</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="6">
-        <v>1</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="6">
-        <v>1</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="6">
-        <v>1</v>
-      </c>
-      <c r="G11" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>76</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>79</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>48</v>
@@ -2690,16 +2706,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="5"/>
+      <c r="C13" s="5" t="s">
+        <v>145</v>
+      </c>
       <c r="D13" s="26" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>48</v>
@@ -2707,318 +2725,320 @@
       <c r="F13" s="6">
         <v>1</v>
       </c>
-      <c r="G13" s="29"/>
-    </row>
-    <row r="14" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="27" t="s">
+      <c r="G13" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D14" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="E14" s="27" t="s">
+      <c r="C14" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="6">
         <v>1</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="E15" s="28" t="s">
+    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="9">
-        <v>3</v>
-      </c>
-      <c r="G15" s="31" t="s">
+      <c r="F15" s="6">
+        <v>1</v>
+      </c>
+      <c r="G15" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="E16" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="E16" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="6">
+        <v>1</v>
+      </c>
+      <c r="G16" s="29"/>
+    </row>
+    <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="10">
+        <v>1</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" s="9">
         <v>3</v>
       </c>
-      <c r="G16" s="29" t="s">
+      <c r="G18" s="31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="9">
-        <v>3</v>
-      </c>
-      <c r="G17" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="6">
-        <v>1</v>
-      </c>
-      <c r="G18" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>91</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="E19" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="9">
+        <v>3</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="9">
+        <v>3</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="6">
         <v>1</v>
       </c>
-      <c r="G19" s="29"/>
-    </row>
-    <row r="20" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B20" s="27" t="s">
+      <c r="G21" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B22" s="26" t="s">
         <v>91</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="10">
-        <v>1</v>
-      </c>
-      <c r="G20" s="30"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B21" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="9">
-        <v>3</v>
-      </c>
-      <c r="G21" s="31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>92</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="E22" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="E22" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="6">
+        <v>1</v>
+      </c>
+      <c r="G22" s="29"/>
+    </row>
+    <row r="23" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="10">
+        <v>1</v>
+      </c>
+      <c r="G23" s="30"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="9">
         <v>3</v>
       </c>
-      <c r="G22" s="29" t="s">
+      <c r="G24" s="31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="9">
-        <v>3</v>
-      </c>
-      <c r="G23" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="E24" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" s="6">
-        <v>1</v>
-      </c>
-      <c r="G24" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>157</v>
+        <v>85</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>92</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="E25" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="9">
+        <v>3</v>
+      </c>
+      <c r="G25" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="9">
+        <v>3</v>
+      </c>
+      <c r="G26" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F27" s="6">
         <v>1</v>
       </c>
-      <c r="G25" s="29"/>
-    </row>
-    <row r="26" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
+      <c r="G27" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="26" t="s">
         <v>158</v>
-      </c>
-      <c r="B26" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="E26" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" s="10">
-        <v>1</v>
-      </c>
-      <c r="G26" s="30"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B27" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D27" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="9">
-        <v>3</v>
-      </c>
-      <c r="G27" s="31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>62</v>
       </c>
       <c r="E28" s="26" t="s">
         <v>48</v>
@@ -3026,75 +3046,85 @@
       <c r="F28" s="6">
         <v>1</v>
       </c>
-      <c r="G28" s="29" t="s">
+      <c r="G28" s="29"/>
+    </row>
+    <row r="29" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="10">
+        <v>1</v>
+      </c>
+      <c r="G29" s="30"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="E30" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F30" s="9">
+        <v>3</v>
+      </c>
+      <c r="G30" s="31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B29" s="26" t="s">
+    <row r="31" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D29" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="E29" s="26" t="s">
+      <c r="C31" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E31" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="6">
-        <v>10</v>
-      </c>
-      <c r="G29" s="29" t="s">
+      <c r="F31" s="10">
+        <v>1</v>
+      </c>
+      <c r="G31" s="30" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="B30" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="D30" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>55</v>
-      </c>
-      <c r="F30" s="42">
-        <v>0.99990000000000001</v>
-      </c>
-      <c r="G30" s="30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="12"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="31"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="29"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="12"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="31"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
       <c r="B33" s="26"/>
       <c r="C33" s="5"/>
@@ -3103,7 +3133,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="29"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>
       <c r="B34" s="26"/>
       <c r="C34" s="5"/>
@@ -3112,7 +3142,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="29"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>
       <c r="B35" s="26"/>
       <c r="C35" s="5"/>
@@ -3121,7 +3151,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="29"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>
       <c r="B36" s="26"/>
       <c r="C36" s="5"/>
@@ -3130,7 +3160,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="29"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>
       <c r="B37" s="26"/>
       <c r="C37" s="5"/>
@@ -3139,7 +3169,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="29"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>
       <c r="B38" s="26"/>
       <c r="C38" s="5"/>
@@ -3148,7 +3178,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="29"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>
       <c r="B39" s="26"/>
       <c r="C39" s="5"/>
@@ -3157,7 +3187,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="29"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>
       <c r="B40" s="26"/>
       <c r="C40" s="5"/>
@@ -3166,7 +3196,7 @@
       <c r="F40" s="6"/>
       <c r="G40" s="29"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
       <c r="B41" s="26"/>
       <c r="C41" s="5"/>
@@ -3175,7 +3205,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
       <c r="B42" s="26"/>
       <c r="C42" s="5"/>
@@ -3184,34 +3214,43 @@
       <c r="F42" s="6"/>
       <c r="G42" s="29"/>
     </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="13"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="29"/>
+    </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F31:F42" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F32:F43" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8 F6 F15:F17 F21:F23 F27" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11 F9 F18:F20 F24:F26 F30" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F9:F14 F18:F20 F24:F26" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12:F17 F21:F23 F27:F29" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
       <formula1>"1, 2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F28" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F31" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
       <formula1>"1, 2, 3"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F29" xr:uid="{42D8AC35-50A5-40BC-BBFA-BE08B273A500}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7" xr:uid="{42D8AC35-50A5-40BC-BBFA-BE08B273A500}">
       <formula1>1</formula1>
       <formula2>20</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F30 F2:F3" xr:uid="{2B8FFCC1-6704-4765-8AD4-006A185633FA}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3 F8" xr:uid="{2B8FFCC1-6704-4765-8AD4-006A185633FA}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5" xr:uid="{758AA2D1-1396-4D76-9384-11AC5DDB0A43}">
-      <formula1>1</formula1>
-      <formula2>100</formula2>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{3A0BB9DE-DDAB-4BD6-B6E2-43F1FC222D8A}">
       <formula1>"1, 2, 3, 4, 5, 6"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F6" xr:uid="{F4E45863-F6B6-49B0-9AF0-77CB1F5B4777}">
+      <formula1>10</formula1>
+      <formula2>1000000</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3221,15 +3260,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -3252,7 +3291,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="72.599999999999994" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>38</v>
       </c>
@@ -3275,7 +3314,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>39</v>
       </c>
@@ -3298,7 +3337,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
@@ -3321,7 +3360,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>44</v>
       </c>
@@ -3344,7 +3383,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>50</v>
       </c>
@@ -3367,7 +3406,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -3390,7 +3429,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>94</v>
       </c>
@@ -3398,10 +3437,10 @@
         <v>23</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>176</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>177</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>55</v>
@@ -3413,7 +3452,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>95</v>
       </c>
@@ -3421,10 +3460,10 @@
         <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>49</v>
@@ -3433,10 +3472,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>96</v>
       </c>
@@ -3444,10 +3483,10 @@
         <v>23</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>112</v>
@@ -3456,10 +3495,10 @@
         <v>20</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>97</v>
       </c>
@@ -3467,10 +3506,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>48</v>
@@ -3482,7 +3521,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
         <v>98</v>
       </c>
@@ -3490,10 +3529,10 @@
         <v>23</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D12" s="27" t="s">
         <v>167</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>168</v>
       </c>
       <c r="E12" s="27" t="s">
         <v>48</v>
@@ -3505,7 +3544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="26"/>
       <c r="C13" s="5"/>
@@ -3514,7 +3553,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -3523,7 +3562,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -3532,7 +3571,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -3541,7 +3580,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -3550,7 +3589,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -3559,7 +3598,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -3568,7 +3607,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -3577,7 +3616,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -3586,7 +3625,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -3595,7 +3634,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -3604,7 +3643,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -3613,7 +3652,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{9401A4D0-A7B1-45F1-8F27-AF31A074385B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EC29174-F32A-4956-87AA-9AFD8E974D87}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1B7590-5493-4A3C-A7B2-6BC5FABEA6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-28920" yWindow="-1470" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="185">
   <si>
     <t>#</t>
   </si>
@@ -629,6 +629,15 @@
   </si>
   <si>
     <t>Kmax</t>
+  </si>
+  <si>
+    <t>Conduction Resistance</t>
+  </si>
+  <si>
+    <t>Temperature dependent coduction resistance</t>
+  </si>
+  <si>
+    <t>Rohm</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1176,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1182,14 +1191,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1227,7 +1232,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1333,7 +1338,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1475,7 +1480,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1484,17 +1489,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA655AC4-52E1-45C0-83AC-CC64B56C05A9}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.6640625" customWidth="1"/>
-    <col min="5" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -1502,7 +1507,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1510,7 +1515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1518,7 +1523,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1526,8 +1531,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -1552,7 +1557,7 @@
       <c r="K13" s="49"/>
       <c r="L13" s="50"/>
     </row>
-    <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -1581,7 +1586,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1593,7 +1598,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -1605,7 +1610,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>4</v>
       </c>
@@ -1617,7 +1622,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>5</v>
       </c>
@@ -1635,21 +1640,24 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"BMW Group Condensed"&amp;12&amp;KC00000 CONFIDENTIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB857B-5D2E-4BE1-B462-B4B5EEAA4370}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -1672,7 +1680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>99</v>
       </c>
@@ -1695,7 +1703,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>100</v>
       </c>
@@ -1718,7 +1726,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>101</v>
       </c>
@@ -1741,7 +1749,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>102</v>
       </c>
@@ -1764,7 +1772,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="13"/>
       <c r="B6" s="26"/>
       <c r="C6" s="5"/>
@@ -1773,7 +1781,7 @@
       <c r="F6" s="6"/>
       <c r="G6" s="29"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
       <c r="B7" s="26"/>
       <c r="C7" s="5"/>
@@ -1782,7 +1790,7 @@
       <c r="F7" s="6"/>
       <c r="G7" s="29"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="26"/>
       <c r="C8" s="5"/>
@@ -1791,7 +1799,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
       <c r="B9" s="26"/>
       <c r="C9" s="5"/>
@@ -1800,7 +1808,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="29"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
       <c r="B10" s="26"/>
       <c r="C10" s="5"/>
@@ -1809,7 +1817,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="26"/>
       <c r="C11" s="5"/>
@@ -1818,7 +1826,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="26"/>
       <c r="C12" s="5"/>
@@ -1827,7 +1835,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="26"/>
       <c r="C13" s="5"/>
@@ -1836,7 +1844,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -1845,7 +1853,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -1854,7 +1862,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -1863,7 +1871,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -1872,7 +1880,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -1881,7 +1889,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -1890,7 +1898,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -1899,7 +1907,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -1908,7 +1916,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -1917,7 +1925,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -1926,7 +1934,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -1935,7 +1943,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -1944,7 +1952,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>
@@ -1953,7 +1961,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="26"/>
       <c r="C27" s="5"/>
@@ -1962,7 +1970,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="26"/>
       <c r="C28" s="5"/>
@@ -1988,21 +1996,24 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"BMW Group Condensed"&amp;12&amp;KC00000 CONFIDENTIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86190CFD-1D2B-4FE4-A04E-A3C453840C86}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2025,7 +2036,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>103</v>
       </c>
@@ -2048,7 +2059,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>104</v>
       </c>
@@ -2071,7 +2082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>107</v>
       </c>
@@ -2094,7 +2105,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>121</v>
       </c>
@@ -2117,7 +2128,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>122</v>
       </c>
@@ -2140,7 +2151,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>123</v>
       </c>
@@ -2163,7 +2174,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>124</v>
       </c>
@@ -2186,7 +2197,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>125</v>
       </c>
@@ -2209,7 +2220,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>126</v>
       </c>
@@ -2232,7 +2243,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>113</v>
       </c>
@@ -2255,7 +2266,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="25"/>
       <c r="C12" s="5"/>
@@ -2264,7 +2275,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="25"/>
       <c r="C13" s="5"/>
@@ -2273,7 +2284,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="25"/>
       <c r="C14" s="5"/>
@@ -2282,7 +2293,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="25"/>
       <c r="C15" s="5"/>
@@ -2291,7 +2302,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="25"/>
       <c r="C16" s="5"/>
@@ -2300,7 +2311,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="25"/>
       <c r="C17" s="5"/>
@@ -2309,7 +2320,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="25"/>
       <c r="C18" s="5"/>
@@ -2318,7 +2329,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="25"/>
       <c r="C19" s="5"/>
@@ -2327,7 +2338,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="25"/>
       <c r="C20" s="5"/>
@@ -2336,7 +2347,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="25"/>
       <c r="C21" s="5"/>
@@ -2345,7 +2356,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="25"/>
       <c r="C22" s="5"/>
@@ -2354,7 +2365,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="25"/>
       <c r="C23" s="5"/>
@@ -2363,7 +2374,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="25"/>
       <c r="C24" s="5"/>
@@ -2372,7 +2383,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="25"/>
       <c r="C25" s="5"/>
@@ -2381,7 +2392,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="25"/>
       <c r="C26" s="5"/>
@@ -2390,7 +2401,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="25"/>
       <c r="C27" s="5"/>
@@ -2415,22 +2426,25 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"BMW Group Condensed"&amp;12&amp;KC00000 CONFIDENTIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
   <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2453,7 +2467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>56</v>
       </c>
@@ -2476,7 +2490,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>57</v>
       </c>
@@ -2499,7 +2513,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
@@ -2522,7 +2536,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="38" t="s">
         <v>178</v>
       </c>
@@ -2545,7 +2559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
         <v>59</v>
       </c>
@@ -2568,7 +2582,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>89</v>
       </c>
@@ -2591,7 +2605,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>90</v>
       </c>
@@ -2614,7 +2628,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>72</v>
       </c>
@@ -2637,7 +2651,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -2660,7 +2674,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>71</v>
       </c>
@@ -2683,7 +2697,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>73</v>
       </c>
@@ -2706,7 +2720,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>74</v>
       </c>
@@ -2729,7 +2743,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>75</v>
       </c>
@@ -2752,7 +2766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>76</v>
       </c>
@@ -2775,7 +2789,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>77</v>
       </c>
@@ -2794,7 +2808,7 @@
       </c>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>78</v>
       </c>
@@ -2817,7 +2831,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>81</v>
       </c>
@@ -2838,7 +2852,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>82</v>
       </c>
@@ -2859,7 +2873,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>83</v>
       </c>
@@ -2880,7 +2894,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>76</v>
       </c>
@@ -2903,7 +2917,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>154</v>
       </c>
@@ -2922,7 +2936,7 @@
       </c>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>155</v>
       </c>
@@ -2943,7 +2957,7 @@
       </c>
       <c r="G23" s="30"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>84</v>
       </c>
@@ -2964,7 +2978,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>85</v>
       </c>
@@ -2985,7 +2999,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>86</v>
       </c>
@@ -3006,7 +3020,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>76</v>
       </c>
@@ -3029,7 +3043,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>156</v>
       </c>
@@ -3048,7 +3062,7 @@
       </c>
       <c r="G28" s="29"/>
     </row>
-    <row r="29" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
         <v>157</v>
       </c>
@@ -3069,7 +3083,7 @@
       </c>
       <c r="G29" s="30"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>87</v>
       </c>
@@ -3092,7 +3106,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
         <v>88</v>
       </c>
@@ -3115,7 +3129,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="28"/>
       <c r="C32" s="8"/>
@@ -3124,7 +3138,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="31"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>
       <c r="B33" s="26"/>
       <c r="C33" s="5"/>
@@ -3133,7 +3147,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="29"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>
       <c r="B34" s="26"/>
       <c r="C34" s="5"/>
@@ -3142,7 +3156,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="29"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="26"/>
       <c r="C35" s="5"/>
@@ -3151,7 +3165,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="29"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="13"/>
       <c r="B36" s="26"/>
       <c r="C36" s="5"/>
@@ -3160,7 +3174,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="29"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="26"/>
       <c r="C37" s="5"/>
@@ -3169,7 +3183,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="29"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="26"/>
       <c r="C38" s="5"/>
@@ -3178,7 +3192,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="29"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>
       <c r="B39" s="26"/>
       <c r="C39" s="5"/>
@@ -3187,7 +3201,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="29"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
       <c r="B40" s="26"/>
       <c r="C40" s="5"/>
@@ -3196,7 +3210,7 @@
       <c r="F40" s="6"/>
       <c r="G40" s="29"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="26"/>
       <c r="C41" s="5"/>
@@ -3205,7 +3219,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>
       <c r="B42" s="26"/>
       <c r="C42" s="5"/>
@@ -3214,7 +3228,7 @@
       <c r="F42" s="6"/>
       <c r="G42" s="29"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="26"/>
       <c r="C43" s="5"/>
@@ -3254,21 +3268,24 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"BMW Group Condensed"&amp;12&amp;KC00000 CONFIDENTIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -3291,7 +3308,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="72.599999999999994" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>38</v>
       </c>
@@ -3314,7 +3331,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>39</v>
       </c>
@@ -3337,7 +3354,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
@@ -3360,7 +3377,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>44</v>
       </c>
@@ -3383,7 +3400,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
         <v>50</v>
       </c>
@@ -3406,7 +3423,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -3429,7 +3446,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>94</v>
       </c>
@@ -3452,7 +3469,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>95</v>
       </c>
@@ -3475,85 +3492,99 @@
         <v>172</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F10" s="11">
-        <v>20</v>
+        <v>49</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="F11" s="11">
+        <v>20</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D12" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E12" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F12" s="6">
         <v>0</v>
       </c>
-      <c r="G11" s="29" t="s">
+      <c r="G12" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
+    <row r="13" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B13" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C13" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D13" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E13" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F13" s="10">
         <v>0</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G13" s="30" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="29"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -3562,7 +3593,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -3571,7 +3602,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -3580,7 +3611,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -3589,7 +3620,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -3598,7 +3629,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -3607,7 +3638,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -3616,7 +3647,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -3625,7 +3656,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -3634,7 +3665,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -3643,7 +3674,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -3652,7 +3683,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -3660,6 +3691,15 @@
       <c r="E25" s="26"/>
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="13"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="29"/>
     </row>
   </sheetData>
   <dataValidations count="6">
@@ -3673,17 +3713,20 @@
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11:F12" xr:uid="{BEBAF08F-EDA5-4C4D-BDED-841DA49ED29D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12:F13" xr:uid="{BEBAF08F-EDA5-4C4D-BDED-841DA49ED29D}">
       <formula1>"0, 1"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F9" xr:uid="{A50DEA59-3116-48A6-9A6B-FEC85B06DD9A}">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F9:F10" xr:uid="{A50DEA59-3116-48A6-9A6B-FEC85B06DD9A}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F25" xr:uid="{C68A9EBE-58BC-4060-95BF-8B9C15EAA08F}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F26" xr:uid="{C68A9EBE-58BC-4060-95BF-8B9C15EAA08F}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"BMW Group Condensed"&amp;12&amp;KC00000 CONFIDENTIAL</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1B7590-5493-4A3C-A7B2-6BC5FABEA6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{1A1B7590-5493-4A3C-A7B2-6BC5FABEA6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{804777F3-FA3C-4C1C-964C-7E219E944C85}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1470" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="190">
   <si>
     <t>#</t>
   </si>
@@ -638,6 +638,21 @@
   </si>
   <si>
     <t>Rohm</t>
+  </si>
+  <si>
+    <t>Spatial Sampling X</t>
+  </si>
+  <si>
+    <t>Spatial Sampling Y</t>
+  </si>
+  <si>
+    <t>Spatial sampling in the first dimension x</t>
+  </si>
+  <si>
+    <t>dx</t>
+  </si>
+  <si>
+    <t>dy</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1191,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1192,9 +1207,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1232,7 +1247,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1338,7 +1353,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1480,7 +1495,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1489,17 +1504,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA655AC4-52E1-45C0-83AC-CC64B56C05A9}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.7109375" customWidth="1"/>
-    <col min="5" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.6640625" customWidth="1"/>
+    <col min="5" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -1507,7 +1522,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1515,7 +1530,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1523,7 +1538,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1531,8 +1546,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -1557,7 +1572,7 @@
       <c r="K13" s="49"/>
       <c r="L13" s="50"/>
     </row>
-    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -1586,7 +1601,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1598,7 +1613,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -1610,7 +1625,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>4</v>
       </c>
@@ -1622,7 +1637,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>5</v>
       </c>
@@ -1648,16 +1663,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB857B-5D2E-4BE1-B462-B4B5EEAA4370}">
-  <dimension ref="A1:G28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -1680,7 +1695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>99</v>
       </c>
@@ -1703,7 +1718,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>100</v>
       </c>
@@ -1726,7 +1741,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>101</v>
       </c>
@@ -1749,48 +1764,76 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D7" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E7" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F7" s="6">
         <v>0</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G7" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="29"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="29"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
       <c r="B8" s="26"/>
       <c r="C8" s="5"/>
@@ -1799,7 +1842,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
       <c r="B9" s="26"/>
       <c r="C9" s="5"/>
@@ -1808,7 +1851,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="29"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>
       <c r="B10" s="26"/>
       <c r="C10" s="5"/>
@@ -1817,7 +1860,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="26"/>
       <c r="C11" s="5"/>
@@ -1826,7 +1869,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="26"/>
       <c r="C12" s="5"/>
@@ -1835,7 +1878,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="26"/>
       <c r="C13" s="5"/>
@@ -1844,7 +1887,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -1853,7 +1896,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -1862,7 +1905,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -1871,7 +1914,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -1880,7 +1923,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -1889,7 +1932,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -1898,7 +1941,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -1907,7 +1950,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -1916,7 +1959,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -1925,7 +1968,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -1934,7 +1977,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -1943,7 +1986,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -1952,7 +1995,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>
@@ -1961,7 +2004,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
       <c r="B27" s="26"/>
       <c r="C27" s="5"/>
@@ -1970,7 +2013,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
       <c r="B28" s="26"/>
       <c r="C28" s="5"/>
@@ -1979,18 +2022,36 @@
       <c r="F28" s="6"/>
       <c r="G28" s="29"/>
     </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="13"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="29"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="13"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="29"/>
+    </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3" xr:uid="{430B1703-6328-4CF3-B881-934A515A8E04}">
       <formula1>"1, 2, 3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F28" xr:uid="{1242AC91-46A9-4A75-8126-745ADEF79F36}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:F30" xr:uid="{1242AC91-46A9-4A75-8126-745ADEF79F36}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{A8468154-AECF-4EB2-8B5F-950EAA6989A2}">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F6" xr:uid="{A8468154-AECF-4EB2-8B5F-950EAA6989A2}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5" xr:uid="{CE82E53E-5A7A-4051-9E6E-6A4D5E40EFB4}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7" xr:uid="{CE82E53E-5A7A-4051-9E6E-6A4D5E40EFB4}">
       <formula1>-1</formula1>
     </dataValidation>
   </dataValidations>
@@ -2005,15 +2066,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86190CFD-1D2B-4FE4-A04E-A3C453840C86}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2036,7 +2097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>103</v>
       </c>
@@ -2059,7 +2120,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>104</v>
       </c>
@@ -2082,7 +2143,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>107</v>
       </c>
@@ -2105,7 +2166,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>121</v>
       </c>
@@ -2128,7 +2189,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>122</v>
       </c>
@@ -2151,7 +2212,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>123</v>
       </c>
@@ -2174,7 +2235,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>124</v>
       </c>
@@ -2197,7 +2258,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>125</v>
       </c>
@@ -2220,7 +2281,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>126</v>
       </c>
@@ -2243,7 +2304,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>113</v>
       </c>
@@ -2266,7 +2327,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="25"/>
       <c r="C12" s="5"/>
@@ -2275,7 +2336,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="25"/>
       <c r="C13" s="5"/>
@@ -2284,7 +2345,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="25"/>
       <c r="C14" s="5"/>
@@ -2293,7 +2354,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="25"/>
       <c r="C15" s="5"/>
@@ -2302,7 +2363,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="25"/>
       <c r="C16" s="5"/>
@@ -2311,7 +2372,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="25"/>
       <c r="C17" s="5"/>
@@ -2320,7 +2381,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="25"/>
       <c r="C18" s="5"/>
@@ -2329,7 +2390,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="25"/>
       <c r="C19" s="5"/>
@@ -2338,7 +2399,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="25"/>
       <c r="C20" s="5"/>
@@ -2347,7 +2408,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="25"/>
       <c r="C21" s="5"/>
@@ -2356,7 +2417,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="25"/>
       <c r="C22" s="5"/>
@@ -2365,7 +2426,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="25"/>
       <c r="C23" s="5"/>
@@ -2374,7 +2435,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="25"/>
       <c r="C24" s="5"/>
@@ -2383,7 +2444,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="25"/>
       <c r="C25" s="5"/>
@@ -2392,7 +2453,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="25"/>
       <c r="C26" s="5"/>
@@ -2401,7 +2462,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
       <c r="B27" s="25"/>
       <c r="C27" s="5"/>
@@ -2435,16 +2496,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
   <dimension ref="A1:G43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2467,7 +2528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>56</v>
       </c>
@@ -2490,7 +2551,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>57</v>
       </c>
@@ -2513,7 +2574,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
@@ -2536,7 +2597,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="38" t="s">
         <v>178</v>
       </c>
@@ -2559,7 +2620,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>59</v>
       </c>
@@ -2582,7 +2643,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>89</v>
       </c>
@@ -2605,7 +2666,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>90</v>
       </c>
@@ -2628,7 +2689,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>72</v>
       </c>
@@ -2651,7 +2712,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -2674,7 +2735,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>71</v>
       </c>
@@ -2697,7 +2758,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>73</v>
       </c>
@@ -2720,7 +2781,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>74</v>
       </c>
@@ -2743,7 +2804,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>75</v>
       </c>
@@ -2766,7 +2827,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>76</v>
       </c>
@@ -2789,7 +2850,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>77</v>
       </c>
@@ -2808,7 +2869,7 @@
       </c>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>78</v>
       </c>
@@ -2831,7 +2892,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>81</v>
       </c>
@@ -2852,7 +2913,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>82</v>
       </c>
@@ -2873,7 +2934,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>83</v>
       </c>
@@ -2894,7 +2955,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>76</v>
       </c>
@@ -2917,7 +2978,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>154</v>
       </c>
@@ -2936,7 +2997,7 @@
       </c>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="14" t="s">
         <v>155</v>
       </c>
@@ -2957,7 +3018,7 @@
       </c>
       <c r="G23" s="30"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>84</v>
       </c>
@@ -2978,7 +3039,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>85</v>
       </c>
@@ -2999,7 +3060,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>86</v>
       </c>
@@ -3020,7 +3081,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>76</v>
       </c>
@@ -3043,7 +3104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>156</v>
       </c>
@@ -3062,7 +3123,7 @@
       </c>
       <c r="G28" s="29"/>
     </row>
-    <row r="29" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="14" t="s">
         <v>157</v>
       </c>
@@ -3083,7 +3144,7 @@
       </c>
       <c r="G29" s="30"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
         <v>87</v>
       </c>
@@ -3106,7 +3167,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="14" t="s">
         <v>88</v>
       </c>
@@ -3129,7 +3190,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="12"/>
       <c r="B32" s="28"/>
       <c r="C32" s="8"/>
@@ -3138,7 +3199,7 @@
       <c r="F32" s="9"/>
       <c r="G32" s="31"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
       <c r="B33" s="26"/>
       <c r="C33" s="5"/>
@@ -3147,7 +3208,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="29"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>
       <c r="B34" s="26"/>
       <c r="C34" s="5"/>
@@ -3156,7 +3217,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="29"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>
       <c r="B35" s="26"/>
       <c r="C35" s="5"/>
@@ -3165,7 +3226,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="29"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>
       <c r="B36" s="26"/>
       <c r="C36" s="5"/>
@@ -3174,7 +3235,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="29"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>
       <c r="B37" s="26"/>
       <c r="C37" s="5"/>
@@ -3183,7 +3244,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="29"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>
       <c r="B38" s="26"/>
       <c r="C38" s="5"/>
@@ -3192,7 +3253,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="29"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>
       <c r="B39" s="26"/>
       <c r="C39" s="5"/>
@@ -3201,7 +3262,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="29"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>
       <c r="B40" s="26"/>
       <c r="C40" s="5"/>
@@ -3210,7 +3271,7 @@
       <c r="F40" s="6"/>
       <c r="G40" s="29"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
       <c r="B41" s="26"/>
       <c r="C41" s="5"/>
@@ -3219,7 +3280,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
       <c r="B42" s="26"/>
       <c r="C42" s="5"/>
@@ -3228,7 +3289,7 @@
       <c r="F42" s="6"/>
       <c r="G42" s="29"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>
       <c r="B43" s="26"/>
       <c r="C43" s="5"/>
@@ -3277,15 +3338,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -3308,7 +3369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="72.599999999999994" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>38</v>
       </c>
@@ -3331,7 +3392,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>39</v>
       </c>
@@ -3354,7 +3415,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
@@ -3377,7 +3438,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>44</v>
       </c>
@@ -3400,7 +3461,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>50</v>
       </c>
@@ -3423,7 +3484,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -3446,7 +3507,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>94</v>
       </c>
@@ -3469,7 +3530,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>95</v>
       </c>
@@ -3492,7 +3553,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>182</v>
       </c>
@@ -3515,7 +3576,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>96</v>
       </c>
@@ -3538,7 +3599,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>97</v>
       </c>
@@ -3561,7 +3622,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>98</v>
       </c>
@@ -3584,7 +3645,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -3593,7 +3654,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -3602,7 +3663,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -3611,7 +3672,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -3620,7 +3681,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -3629,7 +3690,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -3638,7 +3699,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -3647,7 +3708,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -3656,7 +3717,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -3665,7 +3726,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -3674,7 +3735,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -3683,7 +3744,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -3692,7 +3753,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{1A1B7590-5493-4A3C-A7B2-6BC5FABEA6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{804777F3-FA3C-4C1C-964C-7E219E944C85}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{1A1B7590-5493-4A3C-A7B2-6BC5FABEA6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD45966B-4162-4967-BA4D-0AEEDCB1E41B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="189">
   <si>
     <t>#</t>
   </si>
@@ -279,12 +279,6 @@
   </si>
   <si>
     <t>Solver Init</t>
-  </si>
-  <si>
-    <t>N4SID Init</t>
-  </si>
-  <si>
-    <t>N4SID Stability</t>
   </si>
   <si>
     <t>ss</t>
@@ -653,6 +647,9 @@
   </si>
   <si>
     <t>dy</t>
+  </si>
+  <si>
+    <t>Stability</t>
   </si>
 </sst>
 </file>
@@ -1204,6 +1201,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1697,19 +1698,19 @@
     </row>
     <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F2" s="6">
         <v>1</v>
@@ -1720,13 +1721,13 @@
     </row>
     <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B3" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D3" s="26" t="s">
         <v>22</v>
@@ -1743,16 +1744,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>49</v>
@@ -1766,16 +1767,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>49</v>
@@ -1784,21 +1785,21 @@
         <v>0.01</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="26" t="s">
         <v>187</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>189</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>49</v>
@@ -1807,24 +1808,24 @@
         <v>0.01</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F7" s="6">
         <v>0</v>
@@ -2099,16 +2100,16 @@
     </row>
     <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E2" s="26" t="s">
         <v>48</v>
@@ -2122,16 +2123,16 @@
     </row>
     <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B3" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E3" s="26" t="s">
         <v>48</v>
@@ -2145,177 +2146,177 @@
     </row>
     <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F4" s="11">
         <v>0</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F5" s="11">
         <v>0</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F6" s="11">
         <v>0</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F7" s="11">
         <v>0</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F8" s="11">
         <v>0</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F9" s="11">
         <v>0</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F10" s="11">
         <v>0</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>48</v>
@@ -2495,7 +2496,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
@@ -2536,7 +2537,7 @@
         <v>63</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D2" s="28" t="s">
         <v>65</v>
@@ -2559,7 +2560,7 @@
         <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D3" s="26" t="s">
         <v>20</v>
@@ -2582,7 +2583,7 @@
         <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>61</v>
@@ -2599,16 +2600,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="38" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B5" s="39" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E5" s="39" t="s">
         <v>48</v>
@@ -2628,7 +2629,7 @@
         <v>63</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D6" s="39" t="s">
         <v>60</v>
@@ -2645,16 +2646,16 @@
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>48</v>
@@ -2668,16 +2669,16 @@
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B8" s="27" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>55</v>
@@ -2700,7 +2701,7 @@
         <v>70</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E9" s="28" t="s">
         <v>48</v>
@@ -2726,7 +2727,7 @@
         <v>67</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F10" s="10">
         <v>0</v>
@@ -2740,13 +2741,13 @@
         <v>71</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E11" s="28" t="s">
         <v>48</v>
@@ -2763,13 +2764,13 @@
         <v>73</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>48</v>
@@ -2786,13 +2787,13 @@
         <v>74</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>48</v>
@@ -2809,10 +2810,10 @@
         <v>75</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>61</v>
@@ -2832,13 +2833,13 @@
         <v>76</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>48</v>
@@ -2850,58 +2851,60 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
+    <row r="16" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="B16" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="C16" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="10">
+        <v>1</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="E16" s="26" t="s">
+      <c r="B17" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="6">
-        <v>1</v>
-      </c>
-      <c r="G16" s="29"/>
-    </row>
-    <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="27" t="s">
-        <v>79</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="10">
-        <v>1</v>
-      </c>
-      <c r="G17" s="30" t="s">
+      <c r="F17" s="9">
+        <v>3</v>
+      </c>
+      <c r="G17" s="31" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="8"/>
-      <c r="D18" s="28" t="s">
-        <v>140</v>
+      <c r="A18" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="26" t="s">
+        <v>139</v>
       </c>
       <c r="E18" s="28" t="s">
         <v>48</v>
@@ -2909,20 +2912,20 @@
       <c r="F18" s="9">
         <v>3</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="29" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E19" s="28" t="s">
         <v>48</v>
@@ -2934,39 +2937,39 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="5"/>
+        <v>89</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>146</v>
+      </c>
       <c r="D20" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="E20" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="9">
-        <v>3</v>
+      <c r="F20" s="6">
+        <v>1</v>
       </c>
       <c r="G20" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>148</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C21" s="5"/>
       <c r="D21" s="26" t="s">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="E21" s="26" t="s">
         <v>48</v>
@@ -2974,60 +2977,60 @@
       <c r="F21" s="6">
         <v>1</v>
       </c>
-      <c r="G21" s="29" t="s">
+      <c r="G21" s="29"/>
+    </row>
+    <row r="22" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="10">
+        <v>1</v>
+      </c>
+      <c r="G22" s="30"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="9">
+        <v>3</v>
+      </c>
+      <c r="G23" s="31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="6">
-        <v>1</v>
-      </c>
-      <c r="G22" s="29"/>
-    </row>
-    <row r="23" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D23" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="E23" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="10">
-        <v>1</v>
-      </c>
-      <c r="G23" s="30"/>
-    </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="28" t="s">
-        <v>140</v>
+      <c r="A24" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="26" t="s">
+        <v>139</v>
       </c>
       <c r="E24" s="28" t="s">
         <v>48</v>
@@ -3035,20 +3038,20 @@
       <c r="F24" s="9">
         <v>3</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="G24" s="29" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E25" s="28" t="s">
         <v>48</v>
@@ -3060,39 +3063,39 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="5"/>
+        <v>90</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>146</v>
+      </c>
       <c r="D26" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="E26" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F26" s="9">
-        <v>3</v>
+      <c r="F26" s="6">
+        <v>1</v>
       </c>
       <c r="G26" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>148</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="C27" s="5"/>
       <c r="D27" s="26" t="s">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="E27" s="26" t="s">
         <v>48</v>
@@ -3100,104 +3103,92 @@
       <c r="F27" s="6">
         <v>1</v>
       </c>
-      <c r="G27" s="29" t="s">
+      <c r="G27" s="29"/>
+    </row>
+    <row r="28" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="10">
+        <v>1</v>
+      </c>
+      <c r="G28" s="30"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="E29" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="9">
+        <v>3</v>
+      </c>
+      <c r="G29" s="31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="E28" s="26" t="s">
+    <row r="30" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F30" s="10">
         <v>1</v>
       </c>
-      <c r="G28" s="29"/>
-    </row>
-    <row r="29" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="B29" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D29" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="E29" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F29" s="10">
-        <v>1</v>
-      </c>
-      <c r="G29" s="30"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="B30" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="D30" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="E30" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F30" s="9">
-        <v>3</v>
-      </c>
-      <c r="G30" s="31" t="s">
+      <c r="G30" s="30" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B31" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D31" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="E31" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F31" s="10">
-        <v>1</v>
-      </c>
-      <c r="G31" s="30" t="s">
-        <v>16</v>
-      </c>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="12"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="31"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="12"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="31"/>
+      <c r="A32" s="13"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="29"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
@@ -3289,27 +3280,18 @@
       <c r="F42" s="6"/>
       <c r="G42" s="29"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="29"/>
-    </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F32:F43" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F31:F42" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11 F9 F18:F20 F24:F26 F30" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11 F9 F17:F19 F23:F25 F29" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12:F17 F21:F23 F27:F29" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F20:F22 F26:F28 F12:F16" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
       <formula1>"1, 2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F31" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F30" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
       <formula1>"1, 2, 3"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7" xr:uid="{42D8AC35-50A5-40BC-BBFA-BE08B273A500}">
@@ -3509,16 +3491,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B8" s="28" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>55</v>
@@ -3532,16 +3514,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>49</v>
@@ -3550,21 +3532,21 @@
         <v>0</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>49</v>
@@ -3573,44 +3555,44 @@
         <v>0</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F11" s="11">
         <v>20</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>48</v>
@@ -3624,16 +3606,16 @@
     </row>
     <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E13" s="27" t="s">
         <v>48</v>

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{1A1B7590-5493-4A3C-A7B2-6BC5FABEA6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD45966B-4162-4967-BA4D-0AEEDCB1E41B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB165A3-6018-4C71-BD27-378B1911CDB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -1188,7 +1188,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1203,14 +1203,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1248,7 +1244,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1354,7 +1350,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1496,7 +1492,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1505,17 +1501,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA655AC4-52E1-45C0-83AC-CC64B56C05A9}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.6640625" customWidth="1"/>
-    <col min="5" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -1523,7 +1519,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1531,7 +1527,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1539,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1547,8 +1543,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -1573,7 +1569,7 @@
       <c r="K13" s="49"/>
       <c r="L13" s="50"/>
     </row>
-    <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -1602,7 +1598,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1614,7 +1610,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -1626,7 +1622,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>4</v>
       </c>
@@ -1638,7 +1634,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>5</v>
       </c>
@@ -1665,15 +1661,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB857B-5D2E-4BE1-B462-B4B5EEAA4370}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -1696,7 +1692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>97</v>
       </c>
@@ -1713,13 +1709,13 @@
         <v>117</v>
       </c>
       <c r="F2" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>98</v>
       </c>
@@ -1742,7 +1738,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>99</v>
       </c>
@@ -1765,7 +1761,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>183</v>
       </c>
@@ -1788,7 +1784,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>184</v>
       </c>
@@ -1811,7 +1807,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>100</v>
       </c>
@@ -1834,7 +1830,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="26"/>
       <c r="C8" s="5"/>
@@ -1843,7 +1839,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
       <c r="B9" s="26"/>
       <c r="C9" s="5"/>
@@ -1852,7 +1848,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="29"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
       <c r="B10" s="26"/>
       <c r="C10" s="5"/>
@@ -1861,7 +1857,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="26"/>
       <c r="C11" s="5"/>
@@ -1870,7 +1866,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="26"/>
       <c r="C12" s="5"/>
@@ -1879,7 +1875,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="26"/>
       <c r="C13" s="5"/>
@@ -1888,7 +1884,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -1897,7 +1893,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -1906,7 +1902,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -1915,7 +1911,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -1924,7 +1920,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -1933,7 +1929,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -1942,7 +1938,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -1951,7 +1947,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -1960,7 +1956,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -1969,7 +1965,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -1978,7 +1974,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -1987,7 +1983,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -1996,7 +1992,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>
@@ -2005,7 +2001,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="26"/>
       <c r="C27" s="5"/>
@@ -2014,7 +2010,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="26"/>
       <c r="C28" s="5"/>
@@ -2023,7 +2019,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="29"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
       <c r="B29" s="26"/>
       <c r="C29" s="5"/>
@@ -2032,7 +2028,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="29"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
       <c r="B30" s="26"/>
       <c r="C30" s="5"/>
@@ -2067,15 +2063,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86190CFD-1D2B-4FE4-A04E-A3C453840C86}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2098,7 +2094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>101</v>
       </c>
@@ -2121,7 +2117,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>102</v>
       </c>
@@ -2144,7 +2140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>105</v>
       </c>
@@ -2167,7 +2163,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>119</v>
       </c>
@@ -2190,7 +2186,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>120</v>
       </c>
@@ -2213,7 +2209,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>121</v>
       </c>
@@ -2236,7 +2232,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>122</v>
       </c>
@@ -2259,7 +2255,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>123</v>
       </c>
@@ -2282,7 +2278,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>124</v>
       </c>
@@ -2305,7 +2301,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>111</v>
       </c>
@@ -2328,7 +2324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="25"/>
       <c r="C12" s="5"/>
@@ -2337,7 +2333,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="25"/>
       <c r="C13" s="5"/>
@@ -2346,7 +2342,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="25"/>
       <c r="C14" s="5"/>
@@ -2355,7 +2351,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="25"/>
       <c r="C15" s="5"/>
@@ -2364,7 +2360,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="25"/>
       <c r="C16" s="5"/>
@@ -2373,7 +2369,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="25"/>
       <c r="C17" s="5"/>
@@ -2382,7 +2378,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="25"/>
       <c r="C18" s="5"/>
@@ -2391,7 +2387,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="25"/>
       <c r="C19" s="5"/>
@@ -2400,7 +2396,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="25"/>
       <c r="C20" s="5"/>
@@ -2409,7 +2405,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="25"/>
       <c r="C21" s="5"/>
@@ -2418,7 +2414,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="25"/>
       <c r="C22" s="5"/>
@@ -2427,7 +2423,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="25"/>
       <c r="C23" s="5"/>
@@ -2436,7 +2432,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="25"/>
       <c r="C24" s="5"/>
@@ -2445,7 +2441,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="25"/>
       <c r="C25" s="5"/>
@@ -2454,7 +2450,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="25"/>
       <c r="C26" s="5"/>
@@ -2463,7 +2459,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="25"/>
       <c r="C27" s="5"/>
@@ -2497,16 +2493,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2529,7 +2525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>56</v>
       </c>
@@ -2552,7 +2548,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>57</v>
       </c>
@@ -2575,7 +2571,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
@@ -2598,7 +2594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="38" t="s">
         <v>176</v>
       </c>
@@ -2621,7 +2617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
         <v>59</v>
       </c>
@@ -2644,7 +2640,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>87</v>
       </c>
@@ -2667,7 +2663,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>88</v>
       </c>
@@ -2690,7 +2686,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>72</v>
       </c>
@@ -2713,7 +2709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -2736,7 +2732,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>71</v>
       </c>
@@ -2759,7 +2755,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>73</v>
       </c>
@@ -2782,7 +2778,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>74</v>
       </c>
@@ -2805,7 +2801,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>75</v>
       </c>
@@ -2828,7 +2824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>76</v>
       </c>
@@ -2851,7 +2847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>188</v>
       </c>
@@ -2874,7 +2870,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>79</v>
       </c>
@@ -2895,7 +2891,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>80</v>
       </c>
@@ -2916,7 +2912,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>81</v>
       </c>
@@ -2937,7 +2933,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>76</v>
       </c>
@@ -2960,7 +2956,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>152</v>
       </c>
@@ -2979,7 +2975,7 @@
       </c>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
         <v>153</v>
       </c>
@@ -3000,7 +2996,7 @@
       </c>
       <c r="G22" s="30"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>82</v>
       </c>
@@ -3021,7 +3017,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>83</v>
       </c>
@@ -3042,7 +3038,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>84</v>
       </c>
@@ -3063,7 +3059,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>76</v>
       </c>
@@ -3086,7 +3082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>154</v>
       </c>
@@ -3105,7 +3101,7 @@
       </c>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
         <v>155</v>
       </c>
@@ -3126,7 +3122,7 @@
       </c>
       <c r="G28" s="30"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>85</v>
       </c>
@@ -3149,7 +3145,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>86</v>
       </c>
@@ -3172,7 +3168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="28"/>
       <c r="C31" s="8"/>
@@ -3181,7 +3177,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="31"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="13"/>
       <c r="B32" s="26"/>
       <c r="C32" s="5"/>
@@ -3190,7 +3186,7 @@
       <c r="F32" s="6"/>
       <c r="G32" s="29"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="13"/>
       <c r="B33" s="26"/>
       <c r="C33" s="5"/>
@@ -3199,7 +3195,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="29"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="13"/>
       <c r="B34" s="26"/>
       <c r="C34" s="5"/>
@@ -3208,7 +3204,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="29"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="13"/>
       <c r="B35" s="26"/>
       <c r="C35" s="5"/>
@@ -3217,7 +3213,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="29"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="13"/>
       <c r="B36" s="26"/>
       <c r="C36" s="5"/>
@@ -3226,7 +3222,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="29"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="13"/>
       <c r="B37" s="26"/>
       <c r="C37" s="5"/>
@@ -3235,7 +3231,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="29"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="13"/>
       <c r="B38" s="26"/>
       <c r="C38" s="5"/>
@@ -3244,7 +3240,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="29"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="13"/>
       <c r="B39" s="26"/>
       <c r="C39" s="5"/>
@@ -3253,7 +3249,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="29"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
       <c r="B40" s="26"/>
       <c r="C40" s="5"/>
@@ -3262,7 +3258,7 @@
       <c r="F40" s="6"/>
       <c r="G40" s="29"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="26"/>
       <c r="C41" s="5"/>
@@ -3271,7 +3267,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>
       <c r="B42" s="26"/>
       <c r="C42" s="5"/>
@@ -3320,15 +3316,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -3351,7 +3347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="72.599999999999994" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>38</v>
       </c>
@@ -3374,7 +3370,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>39</v>
       </c>
@@ -3397,7 +3393,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
@@ -3420,7 +3416,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>44</v>
       </c>
@@ -3443,7 +3439,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
         <v>50</v>
       </c>
@@ -3466,7 +3462,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -3489,7 +3485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>92</v>
       </c>
@@ -3512,7 +3508,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>93</v>
       </c>
@@ -3535,7 +3531,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>180</v>
       </c>
@@ -3558,7 +3554,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>94</v>
       </c>
@@ -3581,7 +3577,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>95</v>
       </c>
@@ -3604,7 +3600,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>96</v>
       </c>
@@ -3627,7 +3623,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -3636,7 +3632,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -3645,7 +3641,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -3654,7 +3650,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -3663,7 +3659,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -3672,7 +3668,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -3681,7 +3677,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -3690,7 +3686,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -3699,7 +3695,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -3708,7 +3704,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -3717,7 +3713,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -3726,7 +3722,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -3735,7 +3731,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB165A3-6018-4C71-BD27-378B1911CDB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="936" yWindow="1044" windowWidth="17280" windowHeight="9108" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -1501,17 +1501,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA655AC4-52E1-45C0-83AC-CC64B56C05A9}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.7109375" customWidth="1"/>
-    <col min="5" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.6640625" customWidth="1"/>
+    <col min="5" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1543,8 +1543,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="K13" s="49"/>
       <c r="L13" s="50"/>
     </row>
-    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1610,7 +1610,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>4</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>5</v>
       </c>
@@ -1661,15 +1661,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB857B-5D2E-4BE1-B462-B4B5EEAA4370}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>97</v>
       </c>
@@ -1709,13 +1709,13 @@
         <v>117</v>
       </c>
       <c r="F2" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>98</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>99</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>183</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>184</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>100</v>
       </c>
@@ -1824,13 +1824,13 @@
         <v>117</v>
       </c>
       <c r="F7" s="6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G7" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
       <c r="B8" s="26"/>
       <c r="C8" s="5"/>
@@ -1839,7 +1839,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
       <c r="B9" s="26"/>
       <c r="C9" s="5"/>
@@ -1848,7 +1848,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="29"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>
       <c r="B10" s="26"/>
       <c r="C10" s="5"/>
@@ -1857,7 +1857,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="26"/>
       <c r="C11" s="5"/>
@@ -1866,7 +1866,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="26"/>
       <c r="C12" s="5"/>
@@ -1875,7 +1875,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="26"/>
       <c r="C13" s="5"/>
@@ -1884,7 +1884,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -1893,7 +1893,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -1902,7 +1902,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -1911,7 +1911,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -1920,7 +1920,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -1929,7 +1929,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -1938,7 +1938,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -1947,7 +1947,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -1956,7 +1956,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -1965,7 +1965,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -1974,7 +1974,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -1983,7 +1983,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -1992,7 +1992,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>
@@ -2001,7 +2001,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
       <c r="B27" s="26"/>
       <c r="C27" s="5"/>
@@ -2010,7 +2010,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
       <c r="B28" s="26"/>
       <c r="C28" s="5"/>
@@ -2019,7 +2019,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="29"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
       <c r="B29" s="26"/>
       <c r="C29" s="5"/>
@@ -2028,7 +2028,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="29"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="B30" s="26"/>
       <c r="C30" s="5"/>
@@ -2063,15 +2063,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86190CFD-1D2B-4FE4-A04E-A3C453840C86}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>101</v>
       </c>
@@ -2117,7 +2117,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>102</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>105</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>119</v>
       </c>
@@ -2186,7 +2186,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>120</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>121</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>122</v>
       </c>
@@ -2255,7 +2255,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>123</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>124</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>111</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="25"/>
       <c r="C12" s="5"/>
@@ -2333,7 +2333,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="25"/>
       <c r="C13" s="5"/>
@@ -2342,7 +2342,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="25"/>
       <c r="C14" s="5"/>
@@ -2351,7 +2351,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="25"/>
       <c r="C15" s="5"/>
@@ -2360,7 +2360,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="25"/>
       <c r="C16" s="5"/>
@@ -2369,7 +2369,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="25"/>
       <c r="C17" s="5"/>
@@ -2378,7 +2378,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="25"/>
       <c r="C18" s="5"/>
@@ -2387,7 +2387,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="25"/>
       <c r="C19" s="5"/>
@@ -2396,7 +2396,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="25"/>
       <c r="C20" s="5"/>
@@ -2405,7 +2405,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="25"/>
       <c r="C21" s="5"/>
@@ -2414,7 +2414,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="25"/>
       <c r="C22" s="5"/>
@@ -2423,7 +2423,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="25"/>
       <c r="C23" s="5"/>
@@ -2432,7 +2432,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="25"/>
       <c r="C24" s="5"/>
@@ -2441,7 +2441,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="25"/>
       <c r="C25" s="5"/>
@@ -2450,7 +2450,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="25"/>
       <c r="C26" s="5"/>
@@ -2459,7 +2459,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
       <c r="B27" s="25"/>
       <c r="C27" s="5"/>
@@ -2493,16 +2493,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>56</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>57</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="38" t="s">
         <v>176</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>59</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>87</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>88</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>72</v>
       </c>
@@ -2709,7 +2709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>71</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>73</v>
       </c>
@@ -2778,7 +2778,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>74</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>75</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>76</v>
       </c>
@@ -2841,13 +2841,13 @@
         <v>48</v>
       </c>
       <c r="F15" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
         <v>188</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>79</v>
       </c>
@@ -2891,7 +2891,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>80</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>81</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>76</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>152</v>
       </c>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
         <v>153</v>
       </c>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="G22" s="30"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>82</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>83</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>84</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>76</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>154</v>
       </c>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
         <v>155</v>
       </c>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G28" s="30"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>85</v>
       </c>
@@ -3145,7 +3145,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="14" t="s">
         <v>86</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="12"/>
       <c r="B31" s="28"/>
       <c r="C31" s="8"/>
@@ -3177,7 +3177,7 @@
       <c r="F31" s="9"/>
       <c r="G31" s="31"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>
       <c r="B32" s="26"/>
       <c r="C32" s="5"/>
@@ -3186,7 +3186,7 @@
       <c r="F32" s="6"/>
       <c r="G32" s="29"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
       <c r="B33" s="26"/>
       <c r="C33" s="5"/>
@@ -3195,7 +3195,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="29"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>
       <c r="B34" s="26"/>
       <c r="C34" s="5"/>
@@ -3204,7 +3204,7 @@
       <c r="F34" s="6"/>
       <c r="G34" s="29"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>
       <c r="B35" s="26"/>
       <c r="C35" s="5"/>
@@ -3213,7 +3213,7 @@
       <c r="F35" s="6"/>
       <c r="G35" s="29"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>
       <c r="B36" s="26"/>
       <c r="C36" s="5"/>
@@ -3222,7 +3222,7 @@
       <c r="F36" s="6"/>
       <c r="G36" s="29"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>
       <c r="B37" s="26"/>
       <c r="C37" s="5"/>
@@ -3231,7 +3231,7 @@
       <c r="F37" s="6"/>
       <c r="G37" s="29"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>
       <c r="B38" s="26"/>
       <c r="C38" s="5"/>
@@ -3240,7 +3240,7 @@
       <c r="F38" s="6"/>
       <c r="G38" s="29"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>
       <c r="B39" s="26"/>
       <c r="C39" s="5"/>
@@ -3249,7 +3249,7 @@
       <c r="F39" s="6"/>
       <c r="G39" s="29"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>
       <c r="B40" s="26"/>
       <c r="C40" s="5"/>
@@ -3258,7 +3258,7 @@
       <c r="F40" s="6"/>
       <c r="G40" s="29"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
       <c r="B41" s="26"/>
       <c r="C41" s="5"/>
@@ -3267,7 +3267,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
       <c r="B42" s="26"/>
       <c r="C42" s="5"/>
@@ -3316,15 +3316,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -3347,7 +3347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="72.599999999999994" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>38</v>
       </c>
@@ -3370,7 +3370,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>39</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
@@ -3416,7 +3416,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>44</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>50</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>92</v>
       </c>
@@ -3508,7 +3508,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>93</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>180</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>94</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>95</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>96</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -3632,7 +3632,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -3641,7 +3641,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -3650,7 +3650,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -3659,7 +3659,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -3668,7 +3668,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -3677,7 +3677,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -3686,7 +3686,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -3695,7 +3695,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -3704,7 +3704,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -3713,7 +3713,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -3722,7 +3722,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -3731,7 +3731,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC166C76-40D9-4DFB-8DD7-010D2B4E06DB}"/>
   <bookViews>
-    <workbookView xWindow="936" yWindow="1044" windowWidth="17280" windowHeight="9108" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="732" yWindow="4476" windowWidth="23040" windowHeight="12204" activeTab="2" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="186">
   <si>
     <t>#</t>
   </si>
@@ -386,12 +386,6 @@
   </si>
   <si>
     <t>float</t>
-  </si>
-  <si>
-    <t>Data Separation</t>
-  </si>
-  <si>
-    <t>sep</t>
   </si>
   <si>
     <t>m</t>
@@ -604,13 +598,6 @@
   </si>
   <si>
     <t>Rslope</t>
-  </si>
-  <si>
-    <t>Method for separating the data into training, testing, and validation sets:
-1) File based, each set has its own data file
-2) Sheet based, each set has its own excel sheet
-3) ID based, each set has a unique ID from one file
-4) Ratio based, one file is spilt into different parts</t>
   </si>
   <si>
     <t>Maximum Iteration</t>
@@ -1188,7 +1175,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1203,10 +1190,14 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1244,7 +1235,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1350,7 +1341,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1492,7 +1483,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1501,7 +1492,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA655AC4-52E1-45C0-83AC-CC64B56C05A9}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
@@ -1661,7 +1652,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB857B-5D2E-4BE1-B462-B4B5EEAA4370}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
@@ -1700,13 +1691,13 @@
         <v>63</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D2" s="26" t="s">
         <v>78</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F2" s="6">
         <v>2</v>
@@ -1723,7 +1714,7 @@
         <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D3" s="26" t="s">
         <v>22</v>
@@ -1746,16 +1737,16 @@
         <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>49</v>
       </c>
       <c r="F4" s="11">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="G4" s="29" t="s">
         <v>21</v>
@@ -1763,16 +1754,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>49</v>
@@ -1781,21 +1772,21 @@
         <v>0.01</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>49</v>
@@ -1804,7 +1795,7 @@
         <v>0.01</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -1815,16 +1806,16 @@
         <v>63</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F7" s="6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G7" s="29" t="s">
         <v>16</v>
@@ -2062,8 +2053,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86190CFD-1D2B-4FE4-A04E-A3C453840C86}">
-  <dimension ref="A1:G27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.109375" customWidth="1"/>
@@ -2160,21 +2151,21 @@
         <v>0</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>110</v>
@@ -2183,21 +2174,21 @@
         <v>0</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>110</v>
@@ -2206,21 +2197,21 @@
         <v>0</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>110</v>
@@ -2229,21 +2220,21 @@
         <v>0</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>110</v>
@@ -2252,21 +2243,21 @@
         <v>0</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>110</v>
@@ -2275,21 +2266,21 @@
         <v>0</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>110</v>
@@ -2298,31 +2289,17 @@
         <v>0</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="6">
-        <v>2</v>
-      </c>
-      <c r="G11" s="29" t="s">
-        <v>16</v>
-      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="13"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="29"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
@@ -2459,18 +2436,9 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="29"/>
-    </row>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12:F27" xr:uid="{1216C920-F66D-486D-9FEC-8D6771F4D7DB}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11:F26" xr:uid="{1216C920-F66D-486D-9FEC-8D6771F4D7DB}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3" xr:uid="{F91803D7-6ECC-462D-BB39-BF39F2230D48}">
@@ -2478,9 +2446,6 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{83ADC3B0-4649-4A01-9D68-DDE40B796C91}">
       <formula1>"1, 2"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11" xr:uid="{73C737E8-6BB1-4480-A19A-B64640252DD2}">
-      <formula1>"1, 2, 3, 4"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2493,7 +2458,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
   <dimension ref="A1:G42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
@@ -2533,7 +2498,7 @@
         <v>63</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D2" s="28" t="s">
         <v>65</v>
@@ -2556,7 +2521,7 @@
         <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D3" s="26" t="s">
         <v>20</v>
@@ -2579,7 +2544,7 @@
         <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>61</v>
@@ -2596,16 +2561,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="38" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B5" s="39" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E5" s="39" t="s">
         <v>48</v>
@@ -2625,7 +2590,7 @@
         <v>63</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D6" s="39" t="s">
         <v>60</v>
@@ -2648,10 +2613,10 @@
         <v>63</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>48</v>
@@ -2671,10 +2636,10 @@
         <v>63</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>55</v>
@@ -2697,7 +2662,7 @@
         <v>70</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E9" s="28" t="s">
         <v>48</v>
@@ -2740,10 +2705,10 @@
         <v>77</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E11" s="28" t="s">
         <v>48</v>
@@ -2763,10 +2728,10 @@
         <v>77</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>48</v>
@@ -2786,10 +2751,10 @@
         <v>77</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>48</v>
@@ -2809,7 +2774,7 @@
         <v>77</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>61</v>
@@ -2832,7 +2797,7 @@
         <v>77</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D15" s="26" t="s">
         <v>78</v>
@@ -2849,16 +2814,16 @@
     </row>
     <row r="16" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B16" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>48</v>
@@ -2879,7 +2844,7 @@
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E17" s="28" t="s">
         <v>48</v>
@@ -2900,7 +2865,7 @@
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="26" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E18" s="28" t="s">
         <v>48</v>
@@ -2921,7 +2886,7 @@
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="26" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E19" s="28" t="s">
         <v>48</v>
@@ -2941,7 +2906,7 @@
         <v>89</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D20" s="26" t="s">
         <v>78</v>
@@ -2958,14 +2923,14 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B21" s="26" t="s">
         <v>89</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="26" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E21" s="26" t="s">
         <v>48</v>
@@ -2977,16 +2942,16 @@
     </row>
     <row r="22" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B22" s="27" t="s">
         <v>89</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E22" s="27" t="s">
         <v>48</v>
@@ -3005,7 +2970,7 @@
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E23" s="28" t="s">
         <v>48</v>
@@ -3026,7 +2991,7 @@
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="26" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E24" s="28" t="s">
         <v>48</v>
@@ -3047,7 +3012,7 @@
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="26" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E25" s="28" t="s">
         <v>48</v>
@@ -3067,7 +3032,7 @@
         <v>90</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D26" s="26" t="s">
         <v>78</v>
@@ -3084,14 +3049,14 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B27" s="26" t="s">
         <v>90</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="26" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E27" s="26" t="s">
         <v>48</v>
@@ -3103,16 +3068,16 @@
     </row>
     <row r="28" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B28" s="27" t="s">
         <v>90</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E28" s="27" t="s">
         <v>48</v>
@@ -3130,10 +3095,10 @@
         <v>91</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E29" s="28" t="s">
         <v>48</v>
@@ -3153,7 +3118,7 @@
         <v>91</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D30" s="27" t="s">
         <v>62</v>
@@ -3316,7 +3281,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
@@ -3493,10 +3458,10 @@
         <v>23</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>55</v>
@@ -3516,10 +3481,10 @@
         <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>49</v>
@@ -3528,21 +3493,21 @@
         <v>0</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>49</v>
@@ -3551,7 +3516,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -3562,10 +3527,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>110</v>
@@ -3574,7 +3539,7 @@
         <v>20</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
@@ -3585,10 +3550,10 @@
         <v>23</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>48</v>
@@ -3608,10 +3573,10 @@
         <v>23</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E13" s="27" t="s">
         <v>48</v>

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC166C76-40D9-4DFB-8DD7-010D2B4E06DB}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{190F8AAD-AB2E-49F9-9BCA-764A2A64B047}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="4476" windowWidth="23040" windowHeight="12204" activeTab="2" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="170">
   <si>
     <t>#</t>
   </si>
@@ -287,24 +287,6 @@
     <t>init</t>
   </si>
   <si>
-    <t>Model Order TF 1</t>
-  </si>
-  <si>
-    <t>Model Order TF 2</t>
-  </si>
-  <si>
-    <t>Model Order TF 3</t>
-  </si>
-  <si>
-    <t>Model Order AR 1</t>
-  </si>
-  <si>
-    <t>Model Order AR 2</t>
-  </si>
-  <si>
-    <t>Model Order AR 3</t>
-  </si>
-  <si>
     <t>Model Order POD</t>
   </si>
   <si>
@@ -315,12 +297,6 @@
   </si>
   <si>
     <t>Energy Captured</t>
-  </si>
-  <si>
-    <t>tf</t>
-  </si>
-  <si>
-    <t>ar</t>
   </si>
   <si>
     <t>pod</t>
@@ -469,15 +445,6 @@
     <t>K</t>
   </si>
   <si>
-    <t>K1</t>
-  </si>
-  <si>
-    <t>K2</t>
-  </si>
-  <si>
-    <t>K3</t>
-  </si>
-  <si>
     <t>Modeling approach for the SS system:
 1) Discrete using Ts as sample time
 2) Continuous</t>
@@ -520,21 +487,6 @@
   </si>
   <si>
     <t>eng</t>
-  </si>
-  <si>
-    <t>TF Init</t>
-  </si>
-  <si>
-    <t>TF Stability</t>
-  </si>
-  <si>
-    <t>AR Init</t>
-  </si>
-  <si>
-    <t>AR Stability</t>
-  </si>
-  <si>
-    <t>mdlInit</t>
   </si>
   <si>
     <t>Number of POD modes.</t>
@@ -1685,19 +1637,19 @@
     </row>
     <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D2" s="26" t="s">
         <v>78</v>
       </c>
       <c r="E2" s="26" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F2" s="6">
         <v>2</v>
@@ -1708,13 +1660,13 @@
     </row>
     <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B3" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D3" s="26" t="s">
         <v>22</v>
@@ -1731,16 +1683,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E4" s="26" t="s">
         <v>49</v>
@@ -1754,16 +1706,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>49</v>
@@ -1772,21 +1724,21 @@
         <v>0.01</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>49</v>
@@ -1795,24 +1747,24 @@
         <v>0.01</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F7" s="6">
         <v>0</v>
@@ -2087,16 +2039,16 @@
     </row>
     <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D2" s="26" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E2" s="26" t="s">
         <v>48</v>
@@ -2110,16 +2062,16 @@
     </row>
     <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B3" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D3" s="26" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E3" s="26" t="s">
         <v>48</v>
@@ -2133,163 +2085,163 @@
     </row>
     <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F4" s="11">
         <v>0</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F5" s="11">
         <v>0</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F6" s="11">
         <v>0</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F7" s="11">
         <v>0</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F8" s="11">
         <v>0</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F9" s="11">
         <v>0</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F10" s="11">
         <v>0</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2457,7 +2409,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
@@ -2498,7 +2450,7 @@
         <v>63</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="D2" s="28" t="s">
         <v>65</v>
@@ -2521,7 +2473,7 @@
         <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="D3" s="26" t="s">
         <v>20</v>
@@ -2544,7 +2496,7 @@
         <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>61</v>
@@ -2561,16 +2513,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="38" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="B5" s="39" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="D5" s="39" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="E5" s="39" t="s">
         <v>48</v>
@@ -2590,7 +2542,7 @@
         <v>63</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="D6" s="39" t="s">
         <v>60</v>
@@ -2607,16 +2559,16 @@
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>48</v>
@@ -2630,16 +2582,16 @@
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B8" s="27" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>55</v>
@@ -2662,7 +2614,7 @@
         <v>70</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E9" s="28" t="s">
         <v>48</v>
@@ -2688,7 +2640,7 @@
         <v>67</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F10" s="10">
         <v>0</v>
@@ -2705,10 +2657,10 @@
         <v>77</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E11" s="28" t="s">
         <v>48</v>
@@ -2728,10 +2680,10 @@
         <v>77</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>48</v>
@@ -2751,10 +2703,10 @@
         <v>77</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>48</v>
@@ -2774,7 +2726,7 @@
         <v>77</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>61</v>
@@ -2797,7 +2749,7 @@
         <v>77</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D15" s="26" t="s">
         <v>78</v>
@@ -2814,16 +2766,16 @@
     </row>
     <row r="16" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="B16" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>48</v>
@@ -2840,11 +2792,13 @@
         <v>79</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="8"/>
+        <v>83</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>139</v>
+      </c>
       <c r="D17" s="28" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E17" s="28" t="s">
         <v>48</v>
@@ -2856,403 +2810,149 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
+    <row r="18" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="E18" s="28" t="s">
+      <c r="B18" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="9">
-        <v>3</v>
-      </c>
-      <c r="G18" s="29" t="s">
+      <c r="F18" s="10">
+        <v>1</v>
+      </c>
+      <c r="G18" s="30" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="E19" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="9">
-        <v>3</v>
-      </c>
-      <c r="G19" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="6">
-        <v>1</v>
-      </c>
-      <c r="G20" s="29" t="s">
-        <v>16</v>
-      </c>
+      <c r="A19" s="12"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="31"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="13"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="29"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>89</v>
-      </c>
+      <c r="A21" s="13"/>
+      <c r="B21" s="26"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="6">
-        <v>1</v>
-      </c>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="B22" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D22" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="E22" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="10">
-        <v>1</v>
-      </c>
-      <c r="G22" s="30"/>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="13"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="29"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="8"/>
-      <c r="D23" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="9">
-        <v>3</v>
-      </c>
-      <c r="G23" s="31" t="s">
-        <v>16</v>
-      </c>
+      <c r="A23" s="13"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="29"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>90</v>
-      </c>
+      <c r="A24" s="13"/>
+      <c r="B24" s="26"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" s="9">
-        <v>3</v>
-      </c>
-      <c r="G24" s="29" t="s">
-        <v>16</v>
-      </c>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="29"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>90</v>
-      </c>
+      <c r="A25" s="13"/>
+      <c r="B25" s="26"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="E25" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F25" s="9">
-        <v>3</v>
-      </c>
-      <c r="G25" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F26" s="6">
-        <v>1</v>
-      </c>
-      <c r="G26" s="29" t="s">
-        <v>16</v>
-      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="29"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="13"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="29"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>90</v>
-      </c>
+      <c r="A27" s="13"/>
+      <c r="B27" s="26"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="6">
-        <v>1</v>
-      </c>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="6"/>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="B28" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="E28" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F28" s="10">
-        <v>1</v>
-      </c>
-      <c r="G28" s="30"/>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="13"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="29"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B29" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="D29" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="F29" s="9">
-        <v>3</v>
-      </c>
-      <c r="G29" s="31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="B30" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D30" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="F30" s="10">
-        <v>1</v>
-      </c>
-      <c r="G30" s="30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="12"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="31"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="29"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="29"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="29"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="29"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="29"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="29"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="6"/>
-      <c r="G38" s="29"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="29"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="29"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="29"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="29"/>
+      <c r="A29" s="13"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="29"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="13"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="29"/>
     </row>
   </sheetData>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F31:F42" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19:F30" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11 F9 F17:F19 F23:F25 F29" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11 F9 F17" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F20:F22 F26:F28 F12:F16" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12:F16" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
       <formula1>"1, 2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F30" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
       <formula1>"1, 2, 3"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7" xr:uid="{42D8AC35-50A5-40BC-BBFA-BE08B273A500}">
@@ -3452,16 +3152,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B8" s="28" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>55</v>
@@ -3475,16 +3175,16 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>49</v>
@@ -3493,21 +3193,21 @@
         <v>0</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>49</v>
@@ -3516,44 +3216,44 @@
         <v>0</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="F11" s="11">
         <v>20</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>48</v>
@@ -3567,16 +3267,16 @@
     </row>
     <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="E13" s="27" t="s">
         <v>48</v>

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{190F8AAD-AB2E-49F9-9BCA-764A2A64B047}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03AFCBC7-35C7-4BDA-A5AC-0208E3E70427}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="16680" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="201">
   <si>
     <t>#</t>
   </si>
@@ -589,6 +589,110 @@
   </si>
   <si>
     <t>Stability</t>
+  </si>
+  <si>
+    <t>Model Order KNN</t>
+  </si>
+  <si>
+    <t>knn</t>
+  </si>
+  <si>
+    <t>Number of neighbors for KNN</t>
+  </si>
+  <si>
+    <t>NSMethod</t>
+  </si>
+  <si>
+    <t>Distance Metric</t>
+  </si>
+  <si>
+    <t>Distance metric used for computing the distance of a new sample with respect to the KNN space:
+1) 'cityblock', 
+2) 'chebychev', 
+3) 'euclidean', 
+4) 'minkowski'</t>
+  </si>
+  <si>
+    <t>dist</t>
+  </si>
+  <si>
+    <t>ns</t>
+  </si>
+  <si>
+    <t>Neighbor-searcher method:
+1) 'exhaustive'
+2) 'kdtree'</t>
+  </si>
+  <si>
+    <t>MinLeafSize</t>
+  </si>
+  <si>
+    <t>MaxNumSplits</t>
+  </si>
+  <si>
+    <t>MinParentSize</t>
+  </si>
+  <si>
+    <t>leaf</t>
+  </si>
+  <si>
+    <t>split</t>
+  </si>
+  <si>
+    <t>parent</t>
+  </si>
+  <si>
+    <t>dt</t>
+  </si>
+  <si>
+    <t>Limits the maximum number of splits in the tree. This parameter directly controls the depth and complexity of the tree. Lower values reduce the tree size, potentially preventing overfitting</t>
+  </si>
+  <si>
+    <t>Specifies the minimum number of observations per leaf. Increasing MinLeafSize can reduce overfitting by preventing the tree from growing too deep</t>
+  </si>
+  <si>
+    <t>Sets the minimum number of observations in a node for it to be split. Larger values create simpler trees, as nodes with fewer observations are left unsplit.</t>
+  </si>
+  <si>
+    <t>Optimize Free Parameters</t>
+  </si>
+  <si>
+    <t>Automated optimisation of free model parameters:
+0) fixed parameters
+1) optimal parameters</t>
+  </si>
+  <si>
+    <t>opt</t>
+  </si>
+  <si>
+    <t>svm</t>
+  </si>
+  <si>
+    <t>KernelFunction</t>
+  </si>
+  <si>
+    <t>BoxConstraint</t>
+  </si>
+  <si>
+    <t>Epsilon</t>
+  </si>
+  <si>
+    <t>Sets the regularization parameter (C) that controls the trade-off between achieving a low training error and a low testing error (generalization). Higher values lead to fewer support vectors but may overfit.</t>
+  </si>
+  <si>
+    <t>Specifies the epsilon margin in the loss function, which defines a tube within which no penalty is associated with errors.</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Specifies the kernel function to use:
+1) linear
+2) polynomial
+3) rbf</t>
+  </si>
+  <si>
+    <t>kernel</t>
   </si>
 </sst>
 </file>
@@ -662,7 +766,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -999,11 +1103,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1124,6 +1258,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2557,156 +2697,156 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" s="26" t="s">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="B7" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>160</v>
+      <c r="C7" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="D7" s="39" t="s">
+        <v>191</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>48</v>
       </c>
       <c r="F7" s="6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G7" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="14" t="s">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="9">
+        <v>10</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B9" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C9" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D9" s="27" t="s">
         <v>138</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E9" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F9" s="42">
         <v>0.99990000000000001</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G9" s="30" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B10" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D10" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E10" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F10" s="9">
         <v>3</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G10" s="31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="14" t="s">
+    <row r="11" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B11" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D11" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E11" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F11" s="10">
         <v>0</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="G11" s="30" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B12" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C12" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D12" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E12" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F12" s="9">
         <v>3</v>
       </c>
-      <c r="G11" s="31" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="6">
-        <v>1</v>
-      </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="31" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>77</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>48</v>
@@ -2718,18 +2858,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>77</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>48</v>
@@ -2741,187 +2881,325 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>77</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>48</v>
       </c>
       <c r="F15" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="29" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="14" t="s">
+    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="6">
+        <v>2</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B17" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D17" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E17" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F17" s="10">
         <v>1</v>
       </c>
-      <c r="G16" s="30" t="s">
+      <c r="G17" s="30" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B18" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C18" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D18" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E18" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F18" s="9">
         <v>3</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G18" s="31" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="14" t="s">
+    <row r="19" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B19" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C19" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D19" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E19" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F19" s="10">
         <v>1</v>
       </c>
-      <c r="G18" s="30" t="s">
+      <c r="G19" s="30" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="12"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="31"/>
-    </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="29"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="6"/>
+      <c r="A20" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D20" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="9">
+        <v>3</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21" s="6">
+        <v>1</v>
+      </c>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="29"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="29"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="29"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="29"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="29"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="29"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="29"/>
+    <row r="22" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>176</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="6">
+        <v>3</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23" s="9">
+        <v>10</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="E24" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="6">
+        <v>50</v>
+      </c>
+      <c r="G24" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="10">
+        <v>20</v>
+      </c>
+      <c r="G25" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" s="51">
+        <v>1</v>
+      </c>
+      <c r="G26" s="52" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F27" s="9">
+        <v>1</v>
+      </c>
+      <c r="G27" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" s="6">
+        <v>1</v>
+      </c>
+      <c r="G28" s="29" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
@@ -2942,24 +3220,24 @@
       <c r="G30" s="29"/>
     </row>
   </sheetData>
-  <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19:F30" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F29:F30" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11 F9 F17" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12 F10 F18 F20 F25 F23" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12:F16" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F17 F21" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
       <formula1>"1, 2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F18" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19 F26" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
       <formula1>"1, 2, 3"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7" xr:uid="{42D8AC35-50A5-40BC-BBFA-BE08B273A500}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8" xr:uid="{42D8AC35-50A5-40BC-BBFA-BE08B273A500}">
       <formula1>1</formula1>
       <formula2>20</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3 F8" xr:uid="{2B8FFCC1-6704-4765-8AD4-006A185633FA}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F3 F9" xr:uid="{2B8FFCC1-6704-4765-8AD4-006A185633FA}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -2969,6 +3247,18 @@
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F6" xr:uid="{F4E45863-F6B6-49B0-9AF0-77CB1F5B4777}">
       <formula1>10</formula1>
       <formula2>1000000</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7" xr:uid="{6B215F84-9F1B-41AC-8192-16AB63AE3266}">
+      <formula1>"0, 1"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22" xr:uid="{47B450A3-D6D0-4908-B7DA-713464E39E93}">
+      <formula1>"1, 2, 3, 4"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:F28" xr:uid="{E87A8820-6156-4E10-8AF9-95041973A5CF}">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03AFCBC7-35C7-4BDA-A5AC-0208E3E70427}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78A8A145-736B-4EB8-8914-66ECAF6B1CC9}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="16680" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="732" yWindow="4476" windowWidth="23040" windowHeight="12204" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="229">
   <si>
     <t>#</t>
   </si>
@@ -693,6 +693,93 @@
   </si>
   <si>
     <t>kernel</t>
+  </si>
+  <si>
+    <t>MaxEpochs</t>
+  </si>
+  <si>
+    <t>GradientThreshold</t>
+  </si>
+  <si>
+    <t>InitialLearnRate</t>
+  </si>
+  <si>
+    <t>LearnRateDropPeriod</t>
+  </si>
+  <si>
+    <t>LearnRateDropFactor</t>
+  </si>
+  <si>
+    <t>ValidationFrequency</t>
+  </si>
+  <si>
+    <t>dl</t>
+  </si>
+  <si>
+    <t>MiniBatchSize</t>
+  </si>
+  <si>
+    <t>Shuffle</t>
+  </si>
+  <si>
+    <t>ValidationPatience</t>
+  </si>
+  <si>
+    <t>Specifies the maximum number of passes through the entire training dataset. Higher values can lead to better training but also increase the risk of overfitting.</t>
+  </si>
+  <si>
+    <t>Specifies the threshold for gradient clipping to prevent the gradients from exploding. It's useful when training deep networks.</t>
+  </si>
+  <si>
+    <t>epoch</t>
+  </si>
+  <si>
+    <t>gradTh</t>
+  </si>
+  <si>
+    <t>initLr</t>
+  </si>
+  <si>
+    <t>The initial step size for updating the weights. A higher value may speed up learning but can cause instability, while a lower value ensures stable convergence.</t>
+  </si>
+  <si>
+    <t>Specifies the number of epochs between reductions of the learning rate when using the 'piecewise' schedule.</t>
+  </si>
+  <si>
+    <t>Specifies the factor by which the learning rate is reduced. For example, a value of 0.2 means the learning rate is multiplied by 0.2 (i.e., reduced by 80%).</t>
+  </si>
+  <si>
+    <t>lrDropPr</t>
+  </si>
+  <si>
+    <t>lrDropFa</t>
+  </si>
+  <si>
+    <t>Specifies the frequency (in iterations) at which the validation performance is computed. This helps in early stopping and monitoring the progress.</t>
+  </si>
+  <si>
+    <t>valFreq</t>
+  </si>
+  <si>
+    <t>Specifies the number of observations to use in each mini-batch. Smaller sizes can reduce memory usage and allow for more frequent updates.</t>
+  </si>
+  <si>
+    <t>batch</t>
+  </si>
+  <si>
+    <t>Specifies how to shuffle the data before each epoch. Options include 'never', 'once', and 'every-epoch':
+1) never
+2) once
+3) every-epoch</t>
+  </si>
+  <si>
+    <t>shu</t>
+  </si>
+  <si>
+    <t>Specifies the number of epochs with no improvement on the validation data before training is stopped.</t>
+  </si>
+  <si>
+    <t>valPat</t>
   </si>
 </sst>
 </file>
@@ -1250,6 +1337,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1258,12 +1351,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1646,11 +1733,11 @@
       <c r="F13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J13" s="48" t="s">
+      <c r="J13" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="K13" s="49"/>
-      <c r="L13" s="50"/>
+      <c r="K13" s="51"/>
+      <c r="L13" s="52"/>
     </row>
     <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
@@ -2549,7 +2636,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
@@ -3148,10 +3235,10 @@
       <c r="E26" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="F26" s="51">
+      <c r="F26" s="48">
         <v>1</v>
       </c>
-      <c r="G26" s="52" t="s">
+      <c r="G26" s="49" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3178,50 +3265,275 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
+    <row r="28" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="E28" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="10">
         <v>1</v>
       </c>
-      <c r="G28" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="29"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="29"/>
+      <c r="G28" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D29" s="28" t="s">
+        <v>213</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F29" s="6">
+        <v>100</v>
+      </c>
+      <c r="G29" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" s="9">
+        <v>1</v>
+      </c>
+      <c r="G30" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F31" s="9">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>219</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" s="6">
+        <v>50</v>
+      </c>
+      <c r="G32" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="G33" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>222</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" s="6">
+        <v>10</v>
+      </c>
+      <c r="G34" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F35" s="6">
+        <v>64</v>
+      </c>
+      <c r="G35" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" s="6">
+        <v>1</v>
+      </c>
+      <c r="G36" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B37" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D37" s="27" t="s">
+        <v>228</v>
+      </c>
+      <c r="E37" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" s="10">
+        <v>5</v>
+      </c>
+      <c r="G37" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="12"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="31"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="13"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="29"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="13"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="29"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="13"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="29"/>
     </row>
   </sheetData>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F29:F30" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F38:F41" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12 F10 F18 F20 F25 F23" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
@@ -3230,7 +3542,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F17 F21" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
       <formula1>"1, 2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19 F26" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19 F26 F36" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
       <formula1>"1, 2, 3"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8" xr:uid="{42D8AC35-50A5-40BC-BBFA-BE08B273A500}">
@@ -3254,10 +3566,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22" xr:uid="{47B450A3-D6D0-4908-B7DA-713464E39E93}">
       <formula1>"1, 2, 3, 4"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F29 F37 F32 F34:F35" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:F28" xr:uid="{E87A8820-6156-4E10-8AF9-95041973A5CF}">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:F28 F30:F31 F33" xr:uid="{E87A8820-6156-4E10-8AF9-95041973A5CF}">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="189" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78A8A145-736B-4EB8-8914-66ECAF6B1CC9}"/>
+  <xr:revisionPtr revIDLastSave="205" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{988AC640-E210-486E-A3AB-67F7FA6F2076}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="4476" windowWidth="23040" windowHeight="12204" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="3708" yWindow="2940" windowWidth="23040" windowHeight="12204" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="235">
   <si>
     <t>#</t>
   </si>
@@ -780,6 +780,24 @@
   </si>
   <si>
     <t>valPat</t>
+  </si>
+  <si>
+    <t>Window Length</t>
+  </si>
+  <si>
+    <t>Window Strides</t>
+  </si>
+  <si>
+    <t>Length of the input window for sequence to point learning. The input dimension of the model is (FxWxNt) where F are the features, W is the window, and Nt are the number of samples.</t>
+  </si>
+  <si>
+    <t>The strides describe the overab from one window to the next window.</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>stride</t>
   </si>
 </sst>
 </file>
@@ -2636,7 +2654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
@@ -3472,55 +3490,83 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="14" t="s">
+    <row r="37" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="B37" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="C37" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="D37" s="39" t="s">
+        <v>233</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F37" s="6">
+        <v>50</v>
+      </c>
+      <c r="G37" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A38" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="D38" s="39" t="s">
+        <v>234</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="6">
+        <v>1</v>
+      </c>
+      <c r="G38" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B39" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C39" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="D37" s="27" t="s">
+      <c r="D39" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="E37" s="27" t="s">
+      <c r="E39" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F39" s="10">
         <v>5</v>
       </c>
-      <c r="G37" s="30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="12"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="31"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="29"/>
+      <c r="G39" s="30" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="6"/>
-      <c r="G40" s="29"/>
+      <c r="A40" s="12"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="31"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
@@ -3531,12 +3577,30 @@
       <c r="F41" s="6"/>
       <c r="G41" s="29"/>
     </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="13"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="29"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="13"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="29"/>
+    </row>
   </sheetData>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F38:F41" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F40:F43" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12 F10 F18 F20 F25 F23" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12 F10 F18 F20 F25 F23 F38" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F17 F21" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
@@ -3566,7 +3630,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22" xr:uid="{47B450A3-D6D0-4908-B7DA-713464E39E93}">
       <formula1>"1, 2, 3, 4"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F29 F37 F32 F34:F35" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F29 F32 F34:F35 F37 F39" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
       <formula1>1</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:F28 F30:F31 F33" xr:uid="{E87A8820-6156-4E10-8AF9-95041973A5CF}">

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="205" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{988AC640-E210-486E-A3AB-67F7FA6F2076}"/>
   <bookViews>
-    <workbookView xWindow="3708" yWindow="2940" windowWidth="23040" windowHeight="12204" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="14616" yWindow="3084" windowWidth="23040" windowHeight="12204" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="13_ncr:1_{E753D0B1-35F4-4D27-8543-876170205914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{988AC640-E210-486E-A3AB-67F7FA6F2076}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F52FCA0-B855-49F1-9A34-069EE2632F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14616" yWindow="3084" windowWidth="23040" windowHeight="12204" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-28920" yWindow="-1470" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -486,9 +486,6 @@
     <t>Percentag of energy captured through POD modes</t>
   </si>
   <si>
-    <t>eng</t>
-  </si>
-  <si>
     <t>Number of POD modes.</t>
   </si>
   <si>
@@ -798,6 +795,9 @@
   </si>
   <si>
     <t>stride</t>
+  </si>
+  <si>
+    <t>Emax</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1372,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1387,14 +1387,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1432,7 +1428,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1538,7 +1534,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1680,7 +1676,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1689,17 +1685,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA655AC4-52E1-45C0-83AC-CC64B56C05A9}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.6640625" customWidth="1"/>
-    <col min="5" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -1707,7 +1703,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1715,7 +1711,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1723,7 +1719,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1731,8 +1727,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -1757,7 +1753,7 @@
       <c r="K13" s="51"/>
       <c r="L13" s="52"/>
     </row>
-    <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -1786,7 +1782,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1798,7 +1794,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -1810,7 +1806,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>4</v>
       </c>
@@ -1822,7 +1818,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>5</v>
       </c>
@@ -1849,15 +1845,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB857B-5D2E-4BE1-B462-B4B5EEAA4370}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -1880,7 +1876,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>89</v>
       </c>
@@ -1903,7 +1899,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>90</v>
       </c>
@@ -1926,7 +1922,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>91</v>
       </c>
@@ -1949,18 +1945,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="26" t="s">
         <v>166</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>167</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>49</v>
@@ -1972,18 +1968,18 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>49</v>
@@ -1995,7 +1991,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>92</v>
       </c>
@@ -2018,7 +2014,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="26"/>
       <c r="C8" s="5"/>
@@ -2027,7 +2023,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
       <c r="B9" s="26"/>
       <c r="C9" s="5"/>
@@ -2036,7 +2032,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="29"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
       <c r="B10" s="26"/>
       <c r="C10" s="5"/>
@@ -2045,7 +2041,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="26"/>
       <c r="C11" s="5"/>
@@ -2054,7 +2050,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="26"/>
       <c r="C12" s="5"/>
@@ -2063,7 +2059,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="26"/>
       <c r="C13" s="5"/>
@@ -2072,7 +2068,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -2081,7 +2077,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -2090,7 +2086,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -2099,7 +2095,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -2108,7 +2104,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -2117,7 +2113,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -2126,7 +2122,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -2135,7 +2131,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -2144,7 +2140,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -2153,7 +2149,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -2162,7 +2158,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -2171,7 +2167,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -2180,7 +2176,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>
@@ -2189,7 +2185,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
       <c r="B27" s="26"/>
       <c r="C27" s="5"/>
@@ -2198,7 +2194,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13"/>
       <c r="B28" s="26"/>
       <c r="C28" s="5"/>
@@ -2207,7 +2203,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="29"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="13"/>
       <c r="B29" s="26"/>
       <c r="C29" s="5"/>
@@ -2216,7 +2212,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="29"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="13"/>
       <c r="B30" s="26"/>
       <c r="C30" s="5"/>
@@ -2251,15 +2247,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86190CFD-1D2B-4FE4-A04E-A3C453840C86}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2282,7 +2278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>93</v>
       </c>
@@ -2305,7 +2301,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>94</v>
       </c>
@@ -2328,7 +2324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>97</v>
       </c>
@@ -2351,7 +2347,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>109</v>
       </c>
@@ -2374,7 +2370,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>110</v>
       </c>
@@ -2397,7 +2393,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>111</v>
       </c>
@@ -2420,7 +2416,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>112</v>
       </c>
@@ -2443,7 +2439,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>113</v>
       </c>
@@ -2466,7 +2462,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>114</v>
       </c>
@@ -2489,7 +2485,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>
       <c r="B11" s="25"/>
       <c r="C11" s="5"/>
@@ -2498,7 +2494,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>
       <c r="B12" s="25"/>
       <c r="C12" s="5"/>
@@ -2507,7 +2503,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>
       <c r="B13" s="25"/>
       <c r="C13" s="5"/>
@@ -2516,7 +2512,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="25"/>
       <c r="C14" s="5"/>
@@ -2525,7 +2521,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="25"/>
       <c r="C15" s="5"/>
@@ -2534,7 +2530,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="25"/>
       <c r="C16" s="5"/>
@@ -2543,7 +2539,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="25"/>
       <c r="C17" s="5"/>
@@ -2552,7 +2548,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="25"/>
       <c r="C18" s="5"/>
@@ -2561,7 +2557,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="25"/>
       <c r="C19" s="5"/>
@@ -2570,7 +2566,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="25"/>
       <c r="C20" s="5"/>
@@ -2579,7 +2575,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="25"/>
       <c r="C21" s="5"/>
@@ -2588,7 +2584,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="25"/>
       <c r="C22" s="5"/>
@@ -2597,7 +2593,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="25"/>
       <c r="C23" s="5"/>
@@ -2606,7 +2602,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="25"/>
       <c r="C24" s="5"/>
@@ -2615,7 +2611,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="25"/>
       <c r="C25" s="5"/>
@@ -2624,7 +2620,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="25"/>
       <c r="C26" s="5"/>
@@ -2655,16 +2651,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
   <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2687,7 +2683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>56</v>
       </c>
@@ -2695,7 +2691,7 @@
         <v>63</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D2" s="28" t="s">
         <v>65</v>
@@ -2710,7 +2706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>57</v>
       </c>
@@ -2718,7 +2714,7 @@
         <v>63</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D3" s="26" t="s">
         <v>20</v>
@@ -2733,7 +2729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
@@ -2741,7 +2737,7 @@
         <v>63</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D4" s="26" t="s">
         <v>61</v>
@@ -2756,18 +2752,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="38" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B5" s="39" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="39" t="s">
         <v>158</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>159</v>
       </c>
       <c r="E5" s="39" t="s">
         <v>48</v>
@@ -2779,7 +2775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
         <v>59</v>
       </c>
@@ -2787,7 +2783,7 @@
         <v>63</v>
       </c>
       <c r="C6" s="40" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D6" s="39" t="s">
         <v>60</v>
@@ -2802,18 +2798,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="38" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B7" s="39" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="39" t="s">
         <v>190</v>
-      </c>
-      <c r="D7" s="39" t="s">
-        <v>191</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>48</v>
@@ -2825,7 +2821,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>81</v>
       </c>
@@ -2836,7 +2832,7 @@
         <v>136</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>48</v>
@@ -2848,7 +2844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>82</v>
       </c>
@@ -2859,7 +2855,7 @@
         <v>137</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>138</v>
+        <v>234</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>55</v>
@@ -2871,7 +2867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>72</v>
       </c>
@@ -2894,7 +2890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>66</v>
       </c>
@@ -2917,7 +2913,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>71</v>
       </c>
@@ -2940,7 +2936,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>73</v>
       </c>
@@ -2963,7 +2959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>74</v>
       </c>
@@ -2986,7 +2982,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>75</v>
       </c>
@@ -3009,7 +3005,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>76</v>
       </c>
@@ -3032,15 +3028,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B17" s="27" t="s">
         <v>77</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D17" s="27" t="s">
         <v>134</v>
@@ -3055,7 +3051,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>79</v>
       </c>
@@ -3063,7 +3059,7 @@
         <v>83</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D18" s="28" t="s">
         <v>127</v>
@@ -3078,7 +3074,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>80</v>
       </c>
@@ -3101,15 +3097,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B20" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="C20" s="8" t="s">
         <v>171</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>172</v>
       </c>
       <c r="D20" s="28" t="s">
         <v>127</v>
@@ -3124,18 +3120,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E21" s="26" t="s">
         <v>48</v>
@@ -3145,18 +3141,18 @@
       </c>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B22" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="26" t="s">
         <v>175</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>176</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>47</v>
@@ -3168,18 +3164,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E23" s="28" t="s">
         <v>48</v>
@@ -3191,18 +3187,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B24" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>186</v>
-      </c>
       <c r="D24" s="26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E24" s="26" t="s">
         <v>48</v>
@@ -3214,18 +3210,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E25" s="27" t="s">
         <v>48</v>
@@ -3237,18 +3233,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C26" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="28" t="s">
         <v>199</v>
-      </c>
-      <c r="D26" s="28" t="s">
-        <v>200</v>
       </c>
       <c r="E26" s="28" t="s">
         <v>47</v>
@@ -3260,18 +3256,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E27" s="26" t="s">
         <v>49</v>
@@ -3283,15 +3279,15 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D28" s="27" t="s">
         <v>20</v>
@@ -3306,18 +3302,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E29" s="26" t="s">
         <v>48</v>
@@ -3329,18 +3325,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E30" s="26" t="s">
         <v>49</v>
@@ -3352,18 +3348,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E31" s="26" t="s">
         <v>49</v>
@@ -3375,18 +3371,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E32" s="26" t="s">
         <v>48</v>
@@ -3398,18 +3394,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D33" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E33" s="26" t="s">
         <v>49</v>
@@ -3421,18 +3417,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="B34" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="B34" s="26" t="s">
-        <v>207</v>
-      </c>
       <c r="C34" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D34" s="26" t="s">
         <v>221</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>222</v>
       </c>
       <c r="E34" s="26" t="s">
         <v>48</v>
@@ -3444,18 +3440,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C35" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D35" s="26" t="s">
         <v>223</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>224</v>
       </c>
       <c r="E35" s="26" t="s">
         <v>48</v>
@@ -3467,18 +3463,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C36" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D36" s="26" t="s">
         <v>225</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>226</v>
       </c>
       <c r="E36" s="26" t="s">
         <v>48</v>
@@ -3490,18 +3486,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B37" s="39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C37" s="40" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D37" s="39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E37" s="26" t="s">
         <v>48</v>
@@ -3513,18 +3509,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C38" s="40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D38" s="39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E38" s="26" t="s">
         <v>48</v>
@@ -3536,18 +3532,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C39" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D39" s="27" t="s">
         <v>227</v>
-      </c>
-      <c r="D39" s="27" t="s">
-        <v>228</v>
       </c>
       <c r="E39" s="27" t="s">
         <v>48</v>
@@ -3559,7 +3555,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="28"/>
       <c r="C40" s="8"/>
@@ -3568,7 +3564,7 @@
       <c r="F40" s="9"/>
       <c r="G40" s="31"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="13"/>
       <c r="B41" s="26"/>
       <c r="C41" s="5"/>
@@ -3577,7 +3573,7 @@
       <c r="F41" s="6"/>
       <c r="G41" s="29"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="13"/>
       <c r="B42" s="26"/>
       <c r="C42" s="5"/>
@@ -3586,7 +3582,7 @@
       <c r="F42" s="6"/>
       <c r="G42" s="29"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="13"/>
       <c r="B43" s="26"/>
       <c r="C43" s="5"/>
@@ -3647,15 +3643,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="4" max="5" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -3678,7 +3674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="72.599999999999994" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>38</v>
       </c>
@@ -3701,7 +3697,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>39</v>
       </c>
@@ -3724,7 +3720,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
@@ -3747,7 +3743,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>44</v>
       </c>
@@ -3770,7 +3766,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="38" t="s">
         <v>50</v>
       </c>
@@ -3793,7 +3789,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -3816,7 +3812,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>84</v>
       </c>
@@ -3824,10 +3820,10 @@
         <v>23</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>155</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>156</v>
       </c>
       <c r="E8" s="28" t="s">
         <v>55</v>
@@ -3839,7 +3835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>85</v>
       </c>
@@ -3847,10 +3843,10 @@
         <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>49</v>
@@ -3859,21 +3855,21 @@
         <v>0</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="26" t="s">
         <v>162</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>163</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>49</v>
@@ -3882,10 +3878,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>86</v>
       </c>
@@ -3893,10 +3889,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>102</v>
@@ -3905,10 +3901,10 @@
         <v>20</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>87</v>
       </c>
@@ -3916,10 +3912,10 @@
         <v>23</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>48</v>
@@ -3931,7 +3927,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>88</v>
       </c>
@@ -3939,10 +3935,10 @@
         <v>23</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D13" s="27" t="s">
         <v>146</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>147</v>
       </c>
       <c r="E13" s="27" t="s">
         <v>48</v>
@@ -3954,7 +3950,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -3963,7 +3959,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -3972,7 +3968,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -3981,7 +3977,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -3990,7 +3986,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -3999,7 +3995,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -4008,7 +4004,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -4017,7 +4013,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -4026,7 +4022,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -4035,7 +4031,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -4044,7 +4040,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -4053,7 +4049,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -4062,7 +4058,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>

--- a/config/default.xlsx
+++ b/config/default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\q516645\Desktop\Github_ext\TherMOS\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F52FCA0-B855-49F1-9A34-069EE2632F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{4F52FCA0-B855-49F1-9A34-069EE2632F49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB913290-8124-44AB-A8FB-BDA6D1543034}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1470" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-18120" yWindow="-2550" windowWidth="18240" windowHeight="28440" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="260">
   <si>
     <t>#</t>
   </si>
@@ -798,6 +798,91 @@
   </si>
   <si>
     <t>Emax</t>
+  </si>
+  <si>
+    <t>BasisFunction</t>
+  </si>
+  <si>
+    <t>gpr</t>
+  </si>
+  <si>
+    <t>Explicit basis in the GPR model:
+1) Constant
+2) Linear
+3) Quadratic</t>
+  </si>
+  <si>
+    <t>basis</t>
+  </si>
+  <si>
+    <t>Form of the covariance function, specified as one of the following:
+1) Exponential
+2) Squareexponential</t>
+  </si>
+  <si>
+    <t>IterationLimit</t>
+  </si>
+  <si>
+    <t>Maximum number of block coordinate descent method ("bcd") iterations.</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>Ensemble aggregation method:
+1) LSBoost
+2) Bag</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>LearningCycles</t>
+  </si>
+  <si>
+    <t>Number of ensemble learning cycles</t>
+  </si>
+  <si>
+    <t>cycle</t>
+  </si>
+  <si>
+    <t>nn</t>
+  </si>
+  <si>
+    <t>Maximum number of training iterations</t>
+  </si>
+  <si>
+    <t>NumberLayers</t>
+  </si>
+  <si>
+    <t>Number of fully connected layers in the network.</t>
+  </si>
+  <si>
+    <t>layer</t>
+  </si>
+  <si>
+    <t>NumberNeurons</t>
+  </si>
+  <si>
+    <t>Number of nodes per fully connected layer.</t>
+  </si>
+  <si>
+    <t>nodes</t>
+  </si>
+  <si>
+    <t>Activation</t>
+  </si>
+  <si>
+    <t>Activation functions for the fully connected layers of the neural network model:
+1) relu
+2) tanh
+3) sigmoid</t>
+  </si>
+  <si>
+    <t>act</t>
   </si>
 </sst>
 </file>
@@ -1372,7 +1457,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1388,9 +1473,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1428,7 +1513,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1534,7 +1619,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1676,7 +1761,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1685,17 +1770,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA655AC4-52E1-45C0-83AC-CC64B56C05A9}">
   <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.7109375" customWidth="1"/>
-    <col min="5" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.6640625" customWidth="1"/>
+    <col min="5" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="51.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>4</v>
       </c>
@@ -1703,7 +1788,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
@@ -1711,7 +1796,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
@@ -1719,7 +1804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -1727,8 +1812,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="13" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
@@ -1753,7 +1838,7 @@
       <c r="K13" s="51"/>
       <c r="L13" s="52"/>
     </row>
-    <row r="14" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -1782,7 +1867,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>2</v>
       </c>
@@ -1794,7 +1879,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>3</v>
       </c>
@@ -1806,7 +1891,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>4</v>
       </c>
@@ -1818,7 +1903,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>5</v>
       </c>
@@ -1845,15 +1930,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CAB857B-5D2E-4BE1-B462-B4B5EEAA4370}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -1876,7 +1961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="58.2" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>89</v>
       </c>
@@ -1899,7 +1984,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>90</v>
       </c>
@@ -1922,7 +2007,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>91</v>
       </c>
@@ -1945,7 +2030,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>163</v>
       </c>
@@ -1968,7 +2053,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>164</v>
       </c>
@@ -1991,7 +2076,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>92</v>
       </c>
@@ -2014,7 +2099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="13"/>
       <c r="B8" s="26"/>
       <c r="C8" s="5"/>
@@ -2023,7 +2108,7 @@
       <c r="F8" s="6"/>
       <c r="G8" s="29"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>
       <c r="B9" s="26"/>
       <c r="C9" s="5"/>
@@ -2032,7 +2117,7 @@
       <c r="F9" s="6"/>
       <c r="G9" s="29"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>
       <c r="B10" s="26"/>
       <c r="C10" s="5"/>
@@ -2041,7 +2126,7 @@
       <c r="F10" s="6"/>
       <c r="G10" s="29"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="26"/>
       <c r="C11" s="5"/>
@@ -2050,7 +2135,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="26"/>
       <c r="C12" s="5"/>
@@ -2059,7 +2144,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="26"/>
       <c r="C13" s="5"/>
@@ -2068,7 +2153,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -2077,7 +2162,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -2086,7 +2171,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -2095,7 +2180,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -2104,7 +2189,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -2113,7 +2198,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -2122,7 +2207,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -2131,7 +2216,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -2140,7 +2225,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -2149,7 +2234,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -2158,7 +2243,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -2167,7 +2252,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -2176,7 +2261,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>
@@ -2185,7 +2270,7 @@
       <c r="F26" s="6"/>
       <c r="G26" s="29"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="13"/>
       <c r="B27" s="26"/>
       <c r="C27" s="5"/>
@@ -2194,7 +2279,7 @@
       <c r="F27" s="6"/>
       <c r="G27" s="29"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
       <c r="B28" s="26"/>
       <c r="C28" s="5"/>
@@ -2203,7 +2288,7 @@
       <c r="F28" s="6"/>
       <c r="G28" s="29"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
       <c r="B29" s="26"/>
       <c r="C29" s="5"/>
@@ -2212,7 +2297,7 @@
       <c r="F29" s="6"/>
       <c r="G29" s="29"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="B30" s="26"/>
       <c r="C30" s="5"/>
@@ -2247,15 +2332,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86190CFD-1D2B-4FE4-A04E-A3C453840C86}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2278,7 +2363,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="43.8" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>93</v>
       </c>
@@ -2301,7 +2386,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>94</v>
       </c>
@@ -2324,7 +2409,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>97</v>
       </c>
@@ -2347,7 +2432,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>109</v>
       </c>
@@ -2370,7 +2455,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>110</v>
       </c>
@@ -2393,7 +2478,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>111</v>
       </c>
@@ -2416,7 +2501,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>112</v>
       </c>
@@ -2439,7 +2524,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>113</v>
       </c>
@@ -2462,7 +2547,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>114</v>
       </c>
@@ -2485,7 +2570,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>
       <c r="B11" s="25"/>
       <c r="C11" s="5"/>
@@ -2494,7 +2579,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="29"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>
       <c r="B12" s="25"/>
       <c r="C12" s="5"/>
@@ -2503,7 +2588,7 @@
       <c r="F12" s="6"/>
       <c r="G12" s="29"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="25"/>
       <c r="C13" s="5"/>
@@ -2512,7 +2597,7 @@
       <c r="F13" s="6"/>
       <c r="G13" s="29"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="25"/>
       <c r="C14" s="5"/>
@@ -2521,7 +2606,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="25"/>
       <c r="C15" s="5"/>
@@ -2530,7 +2615,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="25"/>
       <c r="C16" s="5"/>
@@ -2539,7 +2624,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="25"/>
       <c r="C17" s="5"/>
@@ -2548,7 +2633,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="25"/>
       <c r="C18" s="5"/>
@@ -2557,7 +2642,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="25"/>
       <c r="C19" s="5"/>
@@ -2566,7 +2651,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="25"/>
       <c r="C20" s="5"/>
@@ -2575,7 +2660,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="25"/>
       <c r="C21" s="5"/>
@@ -2584,7 +2669,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="25"/>
       <c r="C22" s="5"/>
@@ -2593,7 +2678,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="25"/>
       <c r="C23" s="5"/>
@@ -2602,7 +2687,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="25"/>
       <c r="C24" s="5"/>
@@ -2611,7 +2696,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="25"/>
       <c r="C25" s="5"/>
@@ -2620,7 +2705,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="25"/>
       <c r="C26" s="5"/>
@@ -2650,17 +2735,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
-  <dimension ref="A1:G43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -2683,7 +2768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>56</v>
       </c>
@@ -2706,7 +2791,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>57</v>
       </c>
@@ -2729,7 +2814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>58</v>
       </c>
@@ -2752,7 +2837,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="38" t="s">
         <v>156</v>
       </c>
@@ -2775,7 +2860,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>59</v>
       </c>
@@ -2798,7 +2883,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="s">
         <v>188</v>
       </c>
@@ -2821,7 +2906,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>81</v>
       </c>
@@ -2844,7 +2929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>82</v>
       </c>
@@ -2867,7 +2952,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>72</v>
       </c>
@@ -2890,7 +2975,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>66</v>
       </c>
@@ -2913,7 +2998,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>71</v>
       </c>
@@ -2936,7 +3021,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>73</v>
       </c>
@@ -2959,7 +3044,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>74</v>
       </c>
@@ -2982,7 +3067,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>75</v>
       </c>
@@ -3005,7 +3090,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>76</v>
       </c>
@@ -3028,7 +3113,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>168</v>
       </c>
@@ -3051,7 +3136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>79</v>
       </c>
@@ -3074,7 +3159,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
         <v>80</v>
       </c>
@@ -3097,7 +3182,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>169</v>
       </c>
@@ -3120,7 +3205,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>172</v>
       </c>
@@ -3141,7 +3226,7 @@
       </c>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>173</v>
       </c>
@@ -3164,7 +3249,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>178</v>
       </c>
@@ -3187,7 +3272,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>179</v>
       </c>
@@ -3210,7 +3295,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="14" t="s">
         <v>180</v>
       </c>
@@ -3233,7 +3318,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>192</v>
       </c>
@@ -3256,7 +3341,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>193</v>
       </c>
@@ -3279,7 +3364,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="14" t="s">
         <v>194</v>
       </c>
@@ -3302,7 +3387,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>200</v>
       </c>
@@ -3325,7 +3410,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>201</v>
       </c>
@@ -3348,7 +3433,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>202</v>
       </c>
@@ -3371,7 +3456,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>203</v>
       </c>
@@ -3394,7 +3479,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>204</v>
       </c>
@@ -3417,7 +3502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
         <v>205</v>
       </c>
@@ -3440,7 +3525,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>207</v>
       </c>
@@ -3463,7 +3548,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>208</v>
       </c>
@@ -3486,7 +3571,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="38" t="s">
         <v>228</v>
       </c>
@@ -3509,7 +3594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" s="38" t="s">
         <v>229</v>
       </c>
@@ -3532,7 +3617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="14" t="s">
         <v>209</v>
       </c>
@@ -3555,54 +3640,284 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="12"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="31"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="13"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="29"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="13"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="29"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="13"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="29"/>
+    <row r="40" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" s="48">
+        <v>1</v>
+      </c>
+      <c r="G40" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="E41" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" s="6">
+        <v>1</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="E42" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" s="10">
+        <v>100</v>
+      </c>
+      <c r="G42" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D43" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43" s="9">
+        <v>1</v>
+      </c>
+      <c r="G43" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="E44" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" s="6">
+        <v>100</v>
+      </c>
+      <c r="G44" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F45" s="10">
+        <v>50</v>
+      </c>
+      <c r="G45" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F46" s="9">
+        <v>100</v>
+      </c>
+      <c r="G46" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="E47" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F47" s="6">
+        <v>1</v>
+      </c>
+      <c r="G47" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F48" s="6">
+        <v>50</v>
+      </c>
+      <c r="G48" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A49" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F49" s="9">
+        <v>1</v>
+      </c>
+      <c r="G49" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="13"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="29"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="13"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="29"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="13"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="29"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="13"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="29"/>
     </row>
   </sheetData>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F40:F43" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F50:F53" xr:uid="{F2C780A0-57E0-4A53-BC83-1DFDEF4D5C39}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12 F10 F18 F20 F25 F23 F38" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F17 F21" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F17 F21 F41 F43" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
       <formula1>"1, 2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19 F26 F36" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19 F26 F36 F40 F49 F47" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
       <formula1>"1, 2, 3"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8" xr:uid="{42D8AC35-50A5-40BC-BBFA-BE08B273A500}">
@@ -3626,7 +3941,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22" xr:uid="{47B450A3-D6D0-4908-B7DA-713464E39E93}">
       <formula1>"1, 2, 3, 4"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F29 F32 F34:F35 F37 F39" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F29 F32 F34:F35 F37 F39 F44:F46 F42 F48" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
       <formula1>1</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:F28 F30:F31 F33" xr:uid="{E87A8820-6156-4E10-8AF9-95041973A5CF}">
@@ -3643,15 +3958,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{245B3F0A-B85A-4162-A12D-AC7176B54015}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="37" customWidth="1"/>
+    <col min="1" max="1" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" style="37" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.28515625" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>1</v>
       </c>
@@ -3674,7 +3989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="72.599999999999994" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>38</v>
       </c>
@@ -3697,7 +4012,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>39</v>
       </c>
@@ -3720,7 +4035,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
@@ -3743,7 +4058,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>44</v>
       </c>
@@ -3766,7 +4081,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="s">
         <v>50</v>
       </c>
@@ -3789,7 +4104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>52</v>
       </c>
@@ -3812,7 +4127,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>84</v>
       </c>
@@ -3835,7 +4150,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>85</v>
       </c>
@@ -3858,7 +4173,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>160</v>
       </c>
@@ -3881,7 +4196,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>86</v>
       </c>
@@ -3904,7 +4219,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>87</v>
       </c>
@@ -3927,7 +4242,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>88</v>
       </c>
@@ -3950,7 +4265,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>
       <c r="B14" s="26"/>
       <c r="C14" s="5"/>
@@ -3959,7 +4274,7 @@
       <c r="F14" s="6"/>
       <c r="G14" s="29"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>
       <c r="B15" s="26"/>
       <c r="C15" s="5"/>
@@ -3968,7 +4283,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="29"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="26"/>
       <c r="C16" s="5"/>
@@ -3977,7 +4292,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="29"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>
       <c r="B17" s="26"/>
       <c r="C17" s="5"/>
@@ -3986,7 +4301,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="29"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
       <c r="B18" s="26"/>
       <c r="C18" s="5"/>
@@ -3995,7 +4310,7 @@
       <c r="F18" s="6"/>
       <c r="G18" s="29"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>
       <c r="B19" s="26"/>
       <c r="C19" s="5"/>
@@ -4004,7 +4319,7 @@
       <c r="F19" s="6"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>
       <c r="B20" s="26"/>
       <c r="C20" s="5"/>
@@ -4013,7 +4328,7 @@
       <c r="F20" s="6"/>
       <c r="G20" s="29"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>
       <c r="B21" s="26"/>
       <c r="C21" s="5"/>
@@ -4022,7 +4337,7 @@
       <c r="F21" s="6"/>
       <c r="G21" s="29"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>
       <c r="B22" s="26"/>
       <c r="C22" s="5"/>
@@ -4031,7 +4346,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="29"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>
       <c r="B23" s="26"/>
       <c r="C23" s="5"/>
@@ -4040,7 +4355,7 @@
       <c r="F23" s="6"/>
       <c r="G23" s="29"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>
       <c r="B24" s="26"/>
       <c r="C24" s="5"/>
@@ -4049,7 +4364,7 @@
       <c r="F24" s="6"/>
       <c r="G24" s="29"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>
       <c r="B25" s="26"/>
       <c r="C25" s="5"/>
@@ -4058,7 +4373,7 @@
       <c r="F25" s="6"/>
       <c r="G25" s="29"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>
       <c r="B26" s="26"/>
       <c r="C26" s="5"/>
